--- a/mallar/Protokoll/Protokoll_2019_lag_sv-r_mellan(mall).xlsx
+++ b/mallar/Protokoll/Protokoll_2019_lag_sv-r_mellan(mall).xlsx
@@ -1,123 +1,123 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<x:workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <x:fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <x:workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\episerver\voltige\VoltigeClosedXML\mallar\Protokoll\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D54E0CEE-B78A-46E4-8FB4-DD51AEAB4E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Information" sheetId="27" r:id="rId1"/>
-    <sheet name="Häst, lag" sheetId="30" r:id="rId2"/>
-    <sheet name="Lag grund A" sheetId="22" r:id="rId3"/>
-    <sheet name="Lag grund D" sheetId="17" r:id="rId4"/>
-    <sheet name="Lag grund B" sheetId="18" r:id="rId5"/>
-    <sheet name="Lag kür tekn mellan" sheetId="29" r:id="rId6"/>
-    <sheet name="Lag kür tekn junior" sheetId="6" r:id="rId7"/>
-    <sheet name="Lag kür tekn sr" sheetId="20" r:id="rId8"/>
-    <sheet name="Lag kür art" sheetId="21" r:id="rId9"/>
-    <sheet name="Lag kür art senior" sheetId="31" r:id="rId10"/>
-  </sheets>
-  <externalReferences>
-    <externalReference r:id="rId11"/>
-    <externalReference r:id="rId12"/>
-  </externalReferences>
-  <definedNames>
-    <definedName name="Antal_tävlingsdagar" localSheetId="1">[1]Information!$H$5</definedName>
-    <definedName name="Antal_tävlingsdagar">[2]Information!$H$5</definedName>
-    <definedName name="bord" localSheetId="1">'Häst, lag'!$K$3</definedName>
-    <definedName name="bord" localSheetId="2">'Lag grund A'!$L$3</definedName>
-    <definedName name="bord" localSheetId="4">'Lag grund B'!$L$3</definedName>
-    <definedName name="bord" localSheetId="3">'Lag grund D'!$L$3</definedName>
-    <definedName name="bord" localSheetId="8">'Lag kür art'!$L$3</definedName>
-    <definedName name="bord" localSheetId="9">'Lag kür art senior'!$L$3</definedName>
-    <definedName name="bord" localSheetId="6">'Lag kür tekn junior'!$L$3</definedName>
-    <definedName name="bord" localSheetId="5">'Lag kür tekn mellan'!$L$3</definedName>
-    <definedName name="bord" localSheetId="7">'Lag kür tekn sr'!$L$3</definedName>
-    <definedName name="datum" localSheetId="1">'Häst, lag'!$C$4</definedName>
-    <definedName name="datum" localSheetId="2">'Lag grund A'!$C$4</definedName>
-    <definedName name="datum" localSheetId="4">'Lag grund B'!$C$4</definedName>
-    <definedName name="datum" localSheetId="3">'Lag grund D'!$C$4</definedName>
-    <definedName name="datum" localSheetId="8">'Lag kür art'!$C$4</definedName>
-    <definedName name="datum" localSheetId="9">'Lag kür art senior'!$C$4</definedName>
-    <definedName name="datum" localSheetId="6">'Lag kür tekn junior'!$C$4</definedName>
-    <definedName name="datum" localSheetId="5">'Lag kür tekn mellan'!$C$4</definedName>
-    <definedName name="datum" localSheetId="7">'Lag kür tekn sr'!$C$4</definedName>
-    <definedName name="domare" localSheetId="1">'Häst, lag'!$C$36</definedName>
-    <definedName name="domare" localSheetId="2">'Lag grund A'!$C$33</definedName>
-    <definedName name="domare" localSheetId="4">'Lag grund B'!$C$32</definedName>
-    <definedName name="domare" localSheetId="3">'Lag grund D'!$C$33</definedName>
-    <definedName name="domare" localSheetId="8">'Lag kür art'!$C$27</definedName>
-    <definedName name="domare" localSheetId="9">'Lag kür art senior'!$C$27</definedName>
-    <definedName name="domare" localSheetId="6">'Lag kür tekn junior'!$C$42</definedName>
-    <definedName name="domare" localSheetId="5">'Lag kür tekn mellan'!$C$42</definedName>
-    <definedName name="domare" localSheetId="7">'Lag kür tekn sr'!$C$42</definedName>
-    <definedName name="firstvaulter" localSheetId="1">'Häst, lag'!$H$7</definedName>
-    <definedName name="firstvaulter" localSheetId="2">'Lag grund A'!$I$7</definedName>
-    <definedName name="firstvaulter" localSheetId="4">'Lag grund B'!$I$7</definedName>
-    <definedName name="firstvaulter" localSheetId="3">'Lag grund D'!$I$7</definedName>
-    <definedName name="firstvaulter" localSheetId="8">'Lag kür art'!$I$7</definedName>
-    <definedName name="firstvaulter" localSheetId="9">'Lag kür art senior'!$I$7</definedName>
-    <definedName name="firstvaulter" localSheetId="6">'Lag kür tekn junior'!$I$7</definedName>
-    <definedName name="firstvaulter" localSheetId="5">'Lag kür tekn mellan'!$I$7</definedName>
-    <definedName name="firstvaulter" localSheetId="7">'Lag kür tekn sr'!$I$7</definedName>
-    <definedName name="header" localSheetId="1">'Häst, lag'!$A$2</definedName>
-    <definedName name="id" localSheetId="1">'Häst, lag'!$U$1</definedName>
-    <definedName name="id" localSheetId="2">'Lag grund A'!$U$1</definedName>
-    <definedName name="id" localSheetId="4">'Lag grund B'!$U$1</definedName>
-    <definedName name="id" localSheetId="3">'Lag grund D'!$U$1</definedName>
-    <definedName name="id" localSheetId="8">'Lag kür art'!$U$1</definedName>
-    <definedName name="id" localSheetId="9">'Lag kür art senior'!$U$1</definedName>
-    <definedName name="id" localSheetId="6">'Lag kür tekn junior'!$U$1</definedName>
-    <definedName name="id" localSheetId="5">'Lag kür tekn mellan'!$U$1</definedName>
-    <definedName name="id" localSheetId="7">'Lag kür tekn sr'!$U$1</definedName>
-    <definedName name="klass" localSheetId="1">'Häst, lag'!$K$4</definedName>
-    <definedName name="klass" localSheetId="2">'Lag grund A'!$L$4</definedName>
-    <definedName name="klass" localSheetId="4">'Lag grund B'!$L$4</definedName>
-    <definedName name="klass" localSheetId="3">'Lag grund D'!$L$4</definedName>
-    <definedName name="klass" localSheetId="8">'Lag kür art'!$L$4</definedName>
-    <definedName name="klass" localSheetId="9">'Lag kür art senior'!$L$4</definedName>
-    <definedName name="klass" localSheetId="6">'Lag kür tekn junior'!$L$4</definedName>
-    <definedName name="klass" localSheetId="5">'Lag kür tekn mellan'!$L$4</definedName>
-    <definedName name="klass" localSheetId="7">'Lag kür tekn sr'!$L$4</definedName>
-    <definedName name="moment" localSheetId="1">'Häst, lag'!$K$5</definedName>
-    <definedName name="moment" localSheetId="2">'Lag grund A'!$L$5</definedName>
-    <definedName name="moment" localSheetId="4">'Lag grund B'!$L$5</definedName>
-    <definedName name="moment" localSheetId="3">'Lag grund D'!$L$5</definedName>
-    <definedName name="moment" localSheetId="8">'Lag kür art'!$L$5</definedName>
-    <definedName name="moment" localSheetId="9">'Lag kür art senior'!$L$5</definedName>
-    <definedName name="moment" localSheetId="6">'Lag kür tekn junior'!$L$5</definedName>
-    <definedName name="moment" localSheetId="5">'Lag kür tekn mellan'!$L$5</definedName>
-    <definedName name="moment" localSheetId="7">'Lag kür tekn sr'!$L$5</definedName>
-    <definedName name="result" localSheetId="1">'Häst, lag'!$K$32</definedName>
-    <definedName name="result" localSheetId="2">'Lag grund A'!$L$29</definedName>
-    <definedName name="result" localSheetId="4">'Lag grund B'!$L$29</definedName>
-    <definedName name="result" localSheetId="3">'Lag grund D'!$L$29</definedName>
-    <definedName name="result" localSheetId="8">'Lag kür art'!$L$24</definedName>
-    <definedName name="result" localSheetId="9">'Lag kür art senior'!$L$24</definedName>
-    <definedName name="result" localSheetId="6">'Lag kür tekn junior'!$L$34</definedName>
-    <definedName name="result" localSheetId="5">'Lag kür tekn mellan'!$L$34</definedName>
-    <definedName name="result" localSheetId="7">'Lag kür tekn sr'!$L$35</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Häst, lag'!$A$1:$L$36</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+  <x:bookViews>
+    <x:workbookView xWindow="43080" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </x:bookViews>
+  <x:sheets>
+    <x:sheet name="Information" sheetId="27" r:id="rId1"/>
+    <x:sheet name="Häst, lag" sheetId="30" r:id="rId2"/>
+    <x:sheet name="Lag grund A" sheetId="22" r:id="rId3"/>
+    <x:sheet name="Lag grund D" sheetId="17" r:id="rId4"/>
+    <x:sheet name="Lag grund B" sheetId="18" r:id="rId5"/>
+    <x:sheet name="Lag kür tekn mellan" sheetId="29" r:id="rId6"/>
+    <x:sheet name="Lag kür tekn junior" sheetId="6" r:id="rId7"/>
+    <x:sheet name="Lag kür tekn sr" sheetId="20" r:id="rId8"/>
+    <x:sheet name="Lag kür art" sheetId="21" r:id="rId9"/>
+    <x:sheet name="Lag kür art senior" sheetId="31" r:id="rId10"/>
+  </x:sheets>
+  <x:externalReferences>
+    <x:externalReference r:id="rId11"/>
+    <x:externalReference r:id="rId12"/>
+  </x:externalReferences>
+  <x:definedNames>
+    <x:definedName name="Antal_tävlingsdagar" localSheetId="1">[1]Information!$H$5</x:definedName>
+    <x:definedName name="Antal_tävlingsdagar">[2]Information!$H$5</x:definedName>
+    <x:definedName name="bord" localSheetId="1">'Häst, lag'!$K$3</x:definedName>
+    <x:definedName name="bord" localSheetId="2">'Lag grund A'!$L$3</x:definedName>
+    <x:definedName name="bord" localSheetId="4">'Lag grund B'!$L$3</x:definedName>
+    <x:definedName name="bord" localSheetId="3">'Lag grund D'!$L$3</x:definedName>
+    <x:definedName name="bord" localSheetId="8">'Lag kür art'!$L$3</x:definedName>
+    <x:definedName name="bord" localSheetId="9">'Lag kür art senior'!$L$3</x:definedName>
+    <x:definedName name="bord" localSheetId="6">'Lag kür tekn junior'!$L$3</x:definedName>
+    <x:definedName name="bord" localSheetId="5">'Lag kür tekn mellan'!$L$3</x:definedName>
+    <x:definedName name="bord" localSheetId="7">'Lag kür tekn sr'!$L$3</x:definedName>
+    <x:definedName name="datum" localSheetId="1">'Häst, lag'!$C$4</x:definedName>
+    <x:definedName name="datum" localSheetId="2">'Lag grund A'!$C$4</x:definedName>
+    <x:definedName name="datum" localSheetId="4">'Lag grund B'!$C$4</x:definedName>
+    <x:definedName name="datum" localSheetId="3">'Lag grund D'!$C$4</x:definedName>
+    <x:definedName name="datum" localSheetId="8">'Lag kür art'!$C$4</x:definedName>
+    <x:definedName name="datum" localSheetId="9">'Lag kür art senior'!$C$4</x:definedName>
+    <x:definedName name="datum" localSheetId="6">'Lag kür tekn junior'!$C$4</x:definedName>
+    <x:definedName name="datum" localSheetId="5">'Lag kür tekn mellan'!$C$4</x:definedName>
+    <x:definedName name="datum" localSheetId="7">'Lag kür tekn sr'!$C$4</x:definedName>
+    <x:definedName name="domare" localSheetId="1">'Häst, lag'!$C$36</x:definedName>
+    <x:definedName name="domare" localSheetId="2">'Lag grund A'!$C$33</x:definedName>
+    <x:definedName name="domare" localSheetId="4">'Lag grund B'!$C$32</x:definedName>
+    <x:definedName name="domare" localSheetId="3">'Lag grund D'!$C$33</x:definedName>
+    <x:definedName name="domare" localSheetId="8">'Lag kür art'!$C$27</x:definedName>
+    <x:definedName name="domare" localSheetId="9">'Lag kür art senior'!$C$27</x:definedName>
+    <x:definedName name="domare" localSheetId="6">'Lag kür tekn junior'!$C$42</x:definedName>
+    <x:definedName name="domare" localSheetId="5">'Lag kür tekn mellan'!$C$42</x:definedName>
+    <x:definedName name="domare" localSheetId="7">'Lag kür tekn sr'!$C$42</x:definedName>
+    <x:definedName name="firstvaulter" localSheetId="1">'Häst, lag'!$H$7</x:definedName>
+    <x:definedName name="firstvaulter" localSheetId="2">'Lag grund A'!$I$7</x:definedName>
+    <x:definedName name="firstvaulter" localSheetId="4">'Lag grund B'!$I$7</x:definedName>
+    <x:definedName name="firstvaulter" localSheetId="3">'Lag grund D'!$I$7</x:definedName>
+    <x:definedName name="firstvaulter" localSheetId="8">'Lag kür art'!$I$7</x:definedName>
+    <x:definedName name="firstvaulter" localSheetId="9">'Lag kür art senior'!$I$7</x:definedName>
+    <x:definedName name="firstvaulter" localSheetId="6">'Lag kür tekn junior'!$I$7</x:definedName>
+    <x:definedName name="firstvaulter" localSheetId="5">'Lag kür tekn mellan'!$I$7</x:definedName>
+    <x:definedName name="firstvaulter" localSheetId="7">'Lag kür tekn sr'!$I$7</x:definedName>
+    <x:definedName name="header" localSheetId="1">'Häst, lag'!$A$2</x:definedName>
+    <x:definedName name="id" localSheetId="1">'Häst, lag'!$U$1</x:definedName>
+    <x:definedName name="id" localSheetId="2">'Lag grund A'!$U$1</x:definedName>
+    <x:definedName name="id" localSheetId="4">'Lag grund B'!$U$1</x:definedName>
+    <x:definedName name="id" localSheetId="3">'Lag grund D'!$U$1</x:definedName>
+    <x:definedName name="id" localSheetId="8">'Lag kür art'!$U$1</x:definedName>
+    <x:definedName name="id" localSheetId="9">'Lag kür art senior'!$U$1</x:definedName>
+    <x:definedName name="id" localSheetId="6">'Lag kür tekn junior'!$U$1</x:definedName>
+    <x:definedName name="id" localSheetId="5">'Lag kür tekn mellan'!$U$1</x:definedName>
+    <x:definedName name="id" localSheetId="7">'Lag kür tekn sr'!$U$1</x:definedName>
+    <x:definedName name="klass" localSheetId="1">'Häst, lag'!$K$4</x:definedName>
+    <x:definedName name="klass" localSheetId="2">'Lag grund A'!$L$4</x:definedName>
+    <x:definedName name="klass" localSheetId="4">'Lag grund B'!$L$4</x:definedName>
+    <x:definedName name="klass" localSheetId="3">'Lag grund D'!$L$4</x:definedName>
+    <x:definedName name="klass" localSheetId="8">'Lag kür art'!$L$4</x:definedName>
+    <x:definedName name="klass" localSheetId="9">'Lag kür art senior'!$L$4</x:definedName>
+    <x:definedName name="klass" localSheetId="6">'Lag kür tekn junior'!$L$4</x:definedName>
+    <x:definedName name="klass" localSheetId="5">'Lag kür tekn mellan'!$L$4</x:definedName>
+    <x:definedName name="klass" localSheetId="7">'Lag kür tekn sr'!$L$4</x:definedName>
+    <x:definedName name="moment" localSheetId="1">'Häst, lag'!$K$5</x:definedName>
+    <x:definedName name="moment" localSheetId="2">'Lag grund A'!$L$5</x:definedName>
+    <x:definedName name="moment" localSheetId="4">'Lag grund B'!$L$5</x:definedName>
+    <x:definedName name="moment" localSheetId="3">'Lag grund D'!$L$5</x:definedName>
+    <x:definedName name="moment" localSheetId="8">'Lag kür art'!$L$5</x:definedName>
+    <x:definedName name="moment" localSheetId="9">'Lag kür art senior'!$L$5</x:definedName>
+    <x:definedName name="moment" localSheetId="6">'Lag kür tekn junior'!$L$5</x:definedName>
+    <x:definedName name="moment" localSheetId="5">'Lag kür tekn mellan'!$L$5</x:definedName>
+    <x:definedName name="moment" localSheetId="7">'Lag kür tekn sr'!$L$5</x:definedName>
+    <x:definedName name="result" localSheetId="1">'Häst, lag'!$K$32</x:definedName>
+    <x:definedName name="result" localSheetId="2">'Lag grund A'!$L$29</x:definedName>
+    <x:definedName name="result" localSheetId="4">'Lag grund B'!$L$29</x:definedName>
+    <x:definedName name="result" localSheetId="3">'Lag grund D'!$L$29</x:definedName>
+    <x:definedName name="result" localSheetId="8">'Lag kür art'!$L$24</x:definedName>
+    <x:definedName name="result" localSheetId="9">'Lag kür art senior'!$L$24</x:definedName>
+    <x:definedName name="result" localSheetId="6">'Lag kür tekn junior'!$L$34</x:definedName>
+    <x:definedName name="result" localSheetId="5">'Lag kür tekn mellan'!$L$34</x:definedName>
+    <x:definedName name="result" localSheetId="7">'Lag kür tekn sr'!$L$35</x:definedName>
+    <x:definedName name="_xlnm.Print_Area" localSheetId="1">'Häst, lag'!$A$1:$L$36</x:definedName>
+  </x:definedNames>
+  <x:calcPr calcId="191029"/>
+  <x:extLst>
+    <x:ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
       </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
+    </x:ext>
+  </x:extLst>
+</x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4322,594 +4322,594 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84C25329-D17D-4FF2-BF65-A450782F317F}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L36"/>
-  <sheetFormatPr defaultColWidth="9.06640625" defaultRowHeight="12.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="5.73046875" style="43" customWidth="1"/>
-    <col min="2" max="2" width="8.796875" style="43" customWidth="1"/>
-    <col min="3" max="3" width="10.265625" style="43" customWidth="1"/>
-    <col min="4" max="4" width="10.06640625" style="43" customWidth="1"/>
-    <col min="5" max="5" width="9.796875" style="43" customWidth="1"/>
-    <col min="6" max="7" width="9.9296875" style="43" customWidth="1"/>
-    <col min="8" max="8" width="6.265625" style="43" customWidth="1"/>
-    <col min="9" max="9" width="5.73046875" style="43" customWidth="1"/>
-    <col min="10" max="11" width="7.06640625" style="43" customWidth="1"/>
-    <col min="12" max="12" width="7.265625" style="43" customWidth="1"/>
-    <col min="13" max="16384" width="9.06640625" style="43"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" s="138" customFormat="1" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:12" s="138" customFormat="1" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="139" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="140"/>
-      <c r="H2" s="141" t="s">
-        <v>62</v>
-      </c>
-      <c r="I2" s="142"/>
-      <c r="J2" s="143"/>
-      <c r="K2" s="144"/>
-    </row>
-    <row r="3" spans="1:12" s="138" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="145" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="140"/>
-      <c r="H3" s="141" t="s">
-        <v>63</v>
-      </c>
-      <c r="I3" s="142"/>
-      <c r="J3" s="143"/>
-      <c r="K3" s="144"/>
-    </row>
-    <row r="4" spans="1:12" s="138" customFormat="1" ht="17.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="146" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="146"/>
-      <c r="C4" s="258"/>
-      <c r="D4" s="258"/>
-      <c r="E4" s="147"/>
-      <c r="G4" s="140"/>
-      <c r="H4" s="141" t="s">
-        <v>56</v>
-      </c>
-      <c r="I4" s="142"/>
-      <c r="J4" s="143"/>
-      <c r="K4" s="144"/>
-    </row>
-    <row r="5" spans="1:12" s="138" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="148" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="148"/>
-      <c r="C5" s="256"/>
-      <c r="D5" s="256"/>
-      <c r="E5" s="256"/>
-      <c r="G5" s="140"/>
-      <c r="H5" s="141" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" s="149"/>
-      <c r="J5" s="143"/>
-      <c r="K5" s="144"/>
-    </row>
-    <row r="6" spans="1:12" s="138" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="148" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="148"/>
-      <c r="C6" s="256"/>
-      <c r="D6" s="256"/>
-      <c r="E6" s="256"/>
-      <c r="G6" s="138" t="s">
-        <v>15</v>
-      </c>
-      <c r="K6" s="150"/>
-    </row>
-    <row r="7" spans="1:12" s="138" customFormat="1" ht="17.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="148" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="148"/>
-      <c r="C7" s="151"/>
-      <c r="D7" s="151"/>
-      <c r="E7" s="151"/>
-      <c r="G7" s="146" t="s">
-        <v>0</v>
-      </c>
-      <c r="H7" s="259"/>
-      <c r="I7" s="260"/>
-      <c r="J7" s="260"/>
-      <c r="K7" s="260"/>
-    </row>
-    <row r="8" spans="1:12" s="138" customFormat="1" ht="17.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="146" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="146"/>
-      <c r="C8" s="259"/>
-      <c r="D8" s="259"/>
-      <c r="E8" s="259"/>
-      <c r="G8" s="148" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="256"/>
-      <c r="I8" s="257"/>
-      <c r="J8" s="257"/>
-      <c r="K8" s="257"/>
-    </row>
-    <row r="9" spans="1:12" s="138" customFormat="1" ht="17.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="148" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="148"/>
-      <c r="C9" s="256"/>
-      <c r="D9" s="256"/>
-      <c r="E9" s="256"/>
-      <c r="G9" s="148" t="s">
-        <v>2</v>
-      </c>
-      <c r="H9" s="256"/>
-      <c r="I9" s="257"/>
-      <c r="J9" s="257"/>
-      <c r="K9" s="257"/>
-    </row>
-    <row r="10" spans="1:12" s="138" customFormat="1" ht="17.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="148" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="148"/>
-      <c r="C10" s="256"/>
-      <c r="D10" s="256"/>
-      <c r="E10" s="256"/>
-      <c r="G10" s="148" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="256"/>
-      <c r="I10" s="257"/>
-      <c r="J10" s="257"/>
-      <c r="K10" s="257"/>
-    </row>
-    <row r="11" spans="1:12" s="138" customFormat="1" ht="17.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G11" s="148" t="s">
-        <v>4</v>
-      </c>
-      <c r="H11" s="256"/>
-      <c r="I11" s="257"/>
-      <c r="J11" s="257"/>
-      <c r="K11" s="257"/>
-    </row>
-    <row r="12" spans="1:12" s="138" customFormat="1" ht="17.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C12" s="152"/>
-      <c r="G12" s="148" t="s">
-        <v>5</v>
-      </c>
-      <c r="H12" s="256"/>
-      <c r="I12" s="257"/>
-      <c r="J12" s="257"/>
-      <c r="K12" s="257"/>
-    </row>
-    <row r="13" spans="1:12" s="138" customFormat="1" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C13" s="152"/>
-      <c r="G13" s="153"/>
-      <c r="H13" s="154"/>
-      <c r="I13" s="153"/>
-      <c r="J13" s="153"/>
-      <c r="K13" s="153"/>
-    </row>
-    <row r="14" spans="1:12" ht="12.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="138"/>
-      <c r="B14" s="138"/>
-      <c r="C14" s="155"/>
-      <c r="D14" s="155"/>
-      <c r="E14" s="155"/>
-      <c r="F14" s="155"/>
-      <c r="G14" s="138"/>
-      <c r="H14" s="230" t="s">
-        <v>26</v>
-      </c>
-      <c r="I14" s="231"/>
-      <c r="J14" s="232" t="s">
-        <v>60</v>
-      </c>
-      <c r="K14" s="233"/>
-      <c r="L14" s="234"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="235" t="s">
-        <v>113</v>
-      </c>
-      <c r="B15" s="239" t="s">
-        <v>114</v>
-      </c>
-      <c r="C15" s="240"/>
-      <c r="D15" s="240"/>
-      <c r="E15" s="240"/>
-      <c r="F15" s="240"/>
-      <c r="G15" s="240"/>
-      <c r="H15" s="243"/>
-      <c r="I15" s="244"/>
-      <c r="J15" s="249" t="s">
-        <v>115</v>
-      </c>
-      <c r="K15" s="251">
-        <f>SUM(B20:G20)/6</f>
-        <v>0</v>
-      </c>
-      <c r="L15" s="253">
-        <f>ROUND(K15*0.6,3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="236"/>
-      <c r="B16" s="241"/>
-      <c r="C16" s="242"/>
-      <c r="D16" s="242"/>
-      <c r="E16" s="242"/>
-      <c r="F16" s="242"/>
-      <c r="G16" s="242"/>
-      <c r="H16" s="245"/>
-      <c r="I16" s="246"/>
-      <c r="J16" s="217"/>
-      <c r="K16" s="252"/>
-      <c r="L16" s="254"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="236"/>
-      <c r="B17" s="241"/>
-      <c r="C17" s="242"/>
-      <c r="D17" s="242"/>
-      <c r="E17" s="242"/>
-      <c r="F17" s="242"/>
-      <c r="G17" s="242"/>
-      <c r="H17" s="245"/>
-      <c r="I17" s="246"/>
-      <c r="J17" s="217"/>
-      <c r="K17" s="252"/>
-      <c r="L17" s="254"/>
-    </row>
-    <row r="18" spans="1:12" ht="136.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="236"/>
-      <c r="B18" s="241"/>
-      <c r="C18" s="242"/>
-      <c r="D18" s="242"/>
-      <c r="E18" s="242"/>
-      <c r="F18" s="242"/>
-      <c r="G18" s="242"/>
-      <c r="H18" s="245"/>
-      <c r="I18" s="246"/>
-      <c r="J18" s="217"/>
-      <c r="K18" s="252"/>
-      <c r="L18" s="254"/>
-    </row>
-    <row r="19" spans="1:12" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="237"/>
-      <c r="B19" s="156" t="s">
-        <v>116</v>
-      </c>
-      <c r="C19" s="157" t="s">
-        <v>117</v>
-      </c>
-      <c r="D19" s="158" t="s">
-        <v>118</v>
-      </c>
-      <c r="E19" s="157" t="s">
-        <v>119</v>
-      </c>
-      <c r="F19" s="157" t="s">
-        <v>120</v>
-      </c>
-      <c r="G19" s="159" t="s">
-        <v>121</v>
-      </c>
-      <c r="H19" s="245"/>
-      <c r="I19" s="246"/>
-      <c r="J19" s="217"/>
-      <c r="K19" s="252"/>
-      <c r="L19" s="254"/>
-    </row>
-    <row r="20" spans="1:12" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="238"/>
-      <c r="B20" s="160"/>
-      <c r="C20" s="161"/>
-      <c r="D20" s="161"/>
-      <c r="E20" s="161"/>
-      <c r="F20" s="161"/>
-      <c r="G20" s="162"/>
-      <c r="H20" s="247"/>
-      <c r="I20" s="248"/>
-      <c r="J20" s="250"/>
-      <c r="K20" s="252"/>
-      <c r="L20" s="255"/>
-    </row>
-    <row r="21" spans="1:12" ht="12.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="194"/>
-      <c r="B21" s="197" t="s">
-        <v>136</v>
-      </c>
-      <c r="C21" s="197"/>
-      <c r="D21" s="197"/>
-      <c r="E21" s="197"/>
-      <c r="F21" s="197"/>
-      <c r="G21" s="197"/>
-      <c r="H21" s="199"/>
-      <c r="I21" s="200"/>
-      <c r="J21" s="205" t="s">
-        <v>7</v>
-      </c>
-      <c r="K21" s="227">
-        <f>SUMPRODUCT(B26:G26,B25:G25)</f>
-        <v>0</v>
-      </c>
-      <c r="L21" s="208">
-        <f>IF((K21-K28)&gt;=0,ROUND((K21-K28)*0.25,3),0.000000000001)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="195"/>
-      <c r="B22" s="198"/>
-      <c r="C22" s="198"/>
-      <c r="D22" s="198"/>
-      <c r="E22" s="198"/>
-      <c r="F22" s="198"/>
-      <c r="G22" s="198"/>
-      <c r="H22" s="201"/>
-      <c r="I22" s="202"/>
-      <c r="J22" s="206"/>
-      <c r="K22" s="228"/>
-      <c r="L22" s="209"/>
-    </row>
-    <row r="23" spans="1:12" ht="53" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="195"/>
-      <c r="B23" s="198"/>
-      <c r="C23" s="198"/>
-      <c r="D23" s="198"/>
-      <c r="E23" s="198"/>
-      <c r="F23" s="198"/>
-      <c r="G23" s="198"/>
-      <c r="H23" s="201"/>
-      <c r="I23" s="202"/>
-      <c r="J23" s="206"/>
-      <c r="K23" s="228"/>
-      <c r="L23" s="209"/>
-    </row>
-    <row r="24" spans="1:12" ht="15.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="195"/>
-      <c r="B24" s="219" t="s">
-        <v>133</v>
-      </c>
-      <c r="C24" s="220"/>
-      <c r="D24" s="221" t="s">
-        <v>134</v>
-      </c>
-      <c r="E24" s="222"/>
-      <c r="F24" s="223" t="s">
-        <v>135</v>
-      </c>
-      <c r="G24" s="224"/>
-      <c r="H24" s="201"/>
-      <c r="I24" s="202"/>
-      <c r="J24" s="206"/>
-      <c r="K24" s="228"/>
-      <c r="L24" s="209"/>
-    </row>
-    <row r="25" spans="1:12" ht="13.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="195"/>
-      <c r="B25" s="225">
-        <v>0.5</v>
-      </c>
-      <c r="C25" s="226"/>
-      <c r="D25" s="181">
-        <v>0.25</v>
-      </c>
-      <c r="E25" s="182"/>
-      <c r="F25" s="183">
-        <v>0.25</v>
-      </c>
-      <c r="G25" s="184"/>
-      <c r="H25" s="201"/>
-      <c r="I25" s="202"/>
-      <c r="J25" s="206"/>
-      <c r="K25" s="228"/>
-      <c r="L25" s="209"/>
-    </row>
-    <row r="26" spans="1:12" ht="28.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="195"/>
-      <c r="B26" s="185"/>
-      <c r="C26" s="186"/>
-      <c r="D26" s="187"/>
-      <c r="E26" s="188"/>
-      <c r="F26" s="186"/>
-      <c r="G26" s="189"/>
-      <c r="H26" s="201"/>
-      <c r="I26" s="202"/>
-      <c r="J26" s="206"/>
-      <c r="K26" s="229"/>
-      <c r="L26" s="209"/>
-    </row>
-    <row r="27" spans="1:12" ht="10.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="195"/>
-      <c r="B27" s="177"/>
-      <c r="C27" s="178"/>
-      <c r="D27" s="179"/>
-      <c r="E27" s="179"/>
-      <c r="F27" s="178"/>
-      <c r="G27" s="180"/>
-      <c r="H27" s="201"/>
-      <c r="I27" s="202"/>
-      <c r="J27" s="206"/>
-      <c r="K27" s="176"/>
-      <c r="L27" s="209"/>
-    </row>
-    <row r="28" spans="1:12" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="196"/>
-      <c r="B28" s="163" t="s">
-        <v>122</v>
-      </c>
-      <c r="C28" s="164"/>
-      <c r="D28" s="164"/>
-      <c r="E28" s="164"/>
-      <c r="F28" s="164"/>
-      <c r="G28" s="164"/>
-      <c r="H28" s="203"/>
-      <c r="I28" s="204"/>
-      <c r="J28" s="207"/>
-      <c r="K28" s="165">
-        <f>SUM(C28:G28)</f>
-        <v>0</v>
-      </c>
-      <c r="L28" s="210"/>
-    </row>
-    <row r="29" spans="1:12" ht="114.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="194" t="s">
-        <v>16</v>
-      </c>
-      <c r="B29" s="197" t="s">
-        <v>137</v>
-      </c>
-      <c r="C29" s="211"/>
-      <c r="D29" s="211"/>
-      <c r="E29" s="211"/>
-      <c r="F29" s="211"/>
-      <c r="G29" s="212"/>
-      <c r="H29" s="213"/>
-      <c r="I29" s="214"/>
-      <c r="J29" s="217" t="s">
-        <v>123</v>
-      </c>
-      <c r="K29" s="166">
-        <v>0</v>
-      </c>
-      <c r="L29" s="190">
-        <f>IF((K29-K30)&gt;=0,ROUND((K29-K30)*0.15,3),0.00000000001)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="196"/>
-      <c r="B30" s="167" t="s">
-        <v>122</v>
-      </c>
-      <c r="C30" s="164"/>
-      <c r="D30" s="164"/>
-      <c r="E30" s="164"/>
-      <c r="F30" s="164"/>
-      <c r="G30" s="164"/>
-      <c r="H30" s="215"/>
-      <c r="I30" s="216"/>
-      <c r="J30" s="218"/>
-      <c r="K30" s="165">
-        <f>SUM(C30:G30)</f>
-        <v>0</v>
-      </c>
-      <c r="L30" s="191"/>
-    </row>
-    <row r="31" spans="1:12" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="44"/>
-      <c r="B31" s="44"/>
-      <c r="C31" s="44"/>
-      <c r="D31" s="44"/>
-      <c r="E31" s="44"/>
-      <c r="F31" s="44"/>
-      <c r="G31" s="44"/>
-      <c r="H31" s="44"/>
-      <c r="K31" s="57"/>
-    </row>
-    <row r="32" spans="1:12" ht="28.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="I32" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="J32" s="46"/>
-      <c r="K32" s="192">
-        <f>SUM(L15:L29)</f>
-        <v>0</v>
-      </c>
-      <c r="L32" s="193"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="169" t="s">
-        <v>18</v>
-      </c>
-      <c r="B36" s="169"/>
-      <c r="C36" s="169"/>
-      <c r="D36" s="169"/>
-      <c r="E36" s="169"/>
-      <c r="F36" s="168"/>
-      <c r="G36" s="138"/>
-      <c r="H36" s="146" t="s">
-        <v>19</v>
-      </c>
-      <c r="I36" s="146"/>
-      <c r="J36" s="146"/>
-      <c r="K36" s="146"/>
-      <c r="L36" s="146"/>
-    </row>
-  </sheetData>
-  <mergeCells count="41">
-    <mergeCell ref="H12:K12"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="H8:K8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="H10:K10"/>
-    <mergeCell ref="H11:K11"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="A15:A20"/>
-    <mergeCell ref="B15:G18"/>
-    <mergeCell ref="H15:I20"/>
-    <mergeCell ref="J15:J20"/>
-    <mergeCell ref="K15:K20"/>
-    <mergeCell ref="L15:L20"/>
-    <mergeCell ref="L29:L30"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A21:A28"/>
-    <mergeCell ref="B21:G23"/>
-    <mergeCell ref="H21:I28"/>
-    <mergeCell ref="J21:J28"/>
-    <mergeCell ref="L21:L28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:G29"/>
-    <mergeCell ref="H29:I30"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="K21:K26"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="decimal" operator="lessThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Endast siffror giltiga" error="Ej giltig siffra_x000a_Kan du ha skrivit komma  istället för punkt eller tvärt om" sqref="C30:G30 C28 D28 E28 F28 G28 F26:G26 D26:E26 B26:C26 K29 B20 C20 D20 E20 F20 G20" xr:uid="{717696C7-3684-477B-A49A-9E6458A0FA01}">
-      <formula1>11</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.47244094488188981" right="0.15748031496062992" top="0.98425196850393704" bottom="0.39370078740157483" header="0.43307086614173229" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId1"/>
-  <headerFooter alignWithMargins="0">
-    <oddHeader>&amp;L&amp;G
-&amp;C&amp;"Verdana,Normal"&amp;12PROTOKOLL FÖR LAGTÄVLAN</oddHeader>
-    <oddFooter>&amp;R2025-03-16</oddFooter>
-  </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
-</worksheet>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{84C25329-D17D-4FF2-BF65-A450782F317F}" mc:Ignorable="x14ac xr xr2 xr3">
+  <x:sheetPr>
+    <x:pageSetUpPr fitToPage="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:L36"/>
+  <x:sheetFormatPr defaultColWidth="9.06640625" defaultRowHeight="12.4" x14ac:dyDescent="0.3"/>
+  <x:cols>
+    <x:col min="1" max="1" width="5.73046875" style="43" customWidth="1"/>
+    <x:col min="2" max="2" width="8.796875" style="43" customWidth="1"/>
+    <x:col min="3" max="3" width="10.265625" style="43" customWidth="1"/>
+    <x:col min="4" max="4" width="10.06640625" style="43" customWidth="1"/>
+    <x:col min="5" max="5" width="9.796875" style="43" customWidth="1"/>
+    <x:col min="6" max="7" width="9.9296875" style="43" customWidth="1"/>
+    <x:col min="8" max="8" width="6.265625" style="43" customWidth="1"/>
+    <x:col min="9" max="9" width="5.73046875" style="43" customWidth="1"/>
+    <x:col min="10" max="11" width="7.06640625" style="43" customWidth="1"/>
+    <x:col min="12" max="12" width="7.265625" style="43" customWidth="1"/>
+    <x:col min="13" max="16384" width="9.06640625" style="43"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:12" s="138" customFormat="1" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <x:row r="2" spans="1:12" s="138" customFormat="1" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <x:c r="A2" s="139" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G2" s="140"/>
+      <x:c r="H2" s="141" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I2" s="142"/>
+      <x:c r="J2" s="143"/>
+      <x:c r="K2" s="144"/>
+    </x:row>
+    <x:row r="3" spans="1:12" s="138" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <x:c r="A3" s="145" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G3" s="140"/>
+      <x:c r="H3" s="141" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="I3" s="142"/>
+      <x:c r="J3" s="143"/>
+      <x:c r="K3" s="144"/>
+    </x:row>
+    <x:row r="4" spans="1:12" s="138" customFormat="1" ht="17.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <x:c r="A4" s="146" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B4" s="146"/>
+      <x:c r="C4" s="258"/>
+      <x:c r="D4" s="258"/>
+      <x:c r="E4" s="147"/>
+      <x:c r="G4" s="140"/>
+      <x:c r="H4" s="141" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="I4" s="142"/>
+      <x:c r="J4" s="143"/>
+      <x:c r="K4" s="144"/>
+    </x:row>
+    <x:row r="5" spans="1:12" s="138" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <x:c r="A5" s="148" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B5" s="148"/>
+      <x:c r="C5" s="256"/>
+      <x:c r="D5" s="256"/>
+      <x:c r="E5" s="256"/>
+      <x:c r="G5" s="140"/>
+      <x:c r="H5" s="141" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I5" s="149"/>
+      <x:c r="J5" s="143"/>
+      <x:c r="K5" s="144"/>
+    </x:row>
+    <x:row r="6" spans="1:12" s="138" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <x:c r="A6" s="148" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B6" s="148"/>
+      <x:c r="C6" s="256"/>
+      <x:c r="D6" s="256"/>
+      <x:c r="E6" s="256"/>
+      <x:c r="G6" s="138" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K6" s="150"/>
+    </x:row>
+    <x:row r="7" spans="1:12" s="138" customFormat="1" ht="17.2" customHeight="1" x14ac:dyDescent="0.3">
+      <x:c r="A7" s="148" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B7" s="148"/>
+      <x:c r="C7" s="151"/>
+      <x:c r="D7" s="151"/>
+      <x:c r="E7" s="151"/>
+      <x:c r="G7" s="146" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H7" s="259"/>
+      <x:c r="I7" s="260"/>
+      <x:c r="J7" s="260"/>
+      <x:c r="K7" s="260"/>
+    </x:row>
+    <x:row r="8" spans="1:12" s="138" customFormat="1" ht="17.2" customHeight="1" x14ac:dyDescent="0.3">
+      <x:c r="A8" s="146" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B8" s="146"/>
+      <x:c r="C8" s="259"/>
+      <x:c r="D8" s="259"/>
+      <x:c r="E8" s="259"/>
+      <x:c r="G8" s="148" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H8" s="256"/>
+      <x:c r="I8" s="257"/>
+      <x:c r="J8" s="257"/>
+      <x:c r="K8" s="257"/>
+    </x:row>
+    <x:row r="9" spans="1:12" s="138" customFormat="1" ht="17.2" customHeight="1" x14ac:dyDescent="0.3">
+      <x:c r="A9" s="148" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B9" s="148"/>
+      <x:c r="C9" s="256"/>
+      <x:c r="D9" s="256"/>
+      <x:c r="E9" s="256"/>
+      <x:c r="G9" s="148" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H9" s="256"/>
+      <x:c r="I9" s="257"/>
+      <x:c r="J9" s="257"/>
+      <x:c r="K9" s="257"/>
+    </x:row>
+    <x:row r="10" spans="1:12" s="138" customFormat="1" ht="17.2" customHeight="1" x14ac:dyDescent="0.3">
+      <x:c r="A10" s="148" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B10" s="148"/>
+      <x:c r="C10" s="256"/>
+      <x:c r="D10" s="256"/>
+      <x:c r="E10" s="256"/>
+      <x:c r="G10" s="148" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H10" s="256"/>
+      <x:c r="I10" s="257"/>
+      <x:c r="J10" s="257"/>
+      <x:c r="K10" s="257"/>
+    </x:row>
+    <x:row r="11" spans="1:12" s="138" customFormat="1" ht="17.2" customHeight="1" x14ac:dyDescent="0.3">
+      <x:c r="G11" s="148" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H11" s="256"/>
+      <x:c r="I11" s="257"/>
+      <x:c r="J11" s="257"/>
+      <x:c r="K11" s="257"/>
+    </x:row>
+    <x:row r="12" spans="1:12" s="138" customFormat="1" ht="17.2" customHeight="1" x14ac:dyDescent="0.3">
+      <x:c r="C12" s="152"/>
+      <x:c r="G12" s="148" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H12" s="256"/>
+      <x:c r="I12" s="257"/>
+      <x:c r="J12" s="257"/>
+      <x:c r="K12" s="257"/>
+    </x:row>
+    <x:row r="13" spans="1:12" s="138" customFormat="1" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <x:c r="C13" s="152"/>
+      <x:c r="G13" s="153"/>
+      <x:c r="H13" s="154"/>
+      <x:c r="I13" s="153"/>
+      <x:c r="J13" s="153"/>
+      <x:c r="K13" s="153"/>
+    </x:row>
+    <x:row r="14" spans="1:12" ht="12.75" thickBot="1" x14ac:dyDescent="0.35">
+      <x:c r="A14" s="138"/>
+      <x:c r="B14" s="138"/>
+      <x:c r="C14" s="155"/>
+      <x:c r="D14" s="155"/>
+      <x:c r="E14" s="155"/>
+      <x:c r="F14" s="155"/>
+      <x:c r="G14" s="138"/>
+      <x:c r="H14" s="230" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I14" s="231"/>
+      <x:c r="J14" s="232" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K14" s="233"/>
+      <x:c r="L14" s="234"/>
+    </x:row>
+    <x:row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <x:c r="A15" s="235" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B15" s="239" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C15" s="240"/>
+      <x:c r="D15" s="240"/>
+      <x:c r="E15" s="240"/>
+      <x:c r="F15" s="240"/>
+      <x:c r="G15" s="240"/>
+      <x:c r="H15" s="243"/>
+      <x:c r="I15" s="244"/>
+      <x:c r="J15" s="249" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="K15" s="251">
+        <x:f>SUM(B20:G20)/6</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L15" s="253">
+        <x:f>ROUND(K15*0.6,3)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <x:c r="A16" s="236"/>
+      <x:c r="B16" s="241"/>
+      <x:c r="C16" s="242"/>
+      <x:c r="D16" s="242"/>
+      <x:c r="E16" s="242"/>
+      <x:c r="F16" s="242"/>
+      <x:c r="G16" s="242"/>
+      <x:c r="H16" s="245"/>
+      <x:c r="I16" s="246"/>
+      <x:c r="J16" s="217"/>
+      <x:c r="K16" s="252"/>
+      <x:c r="L16" s="254"/>
+    </x:row>
+    <x:row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <x:c r="A17" s="236"/>
+      <x:c r="B17" s="241"/>
+      <x:c r="C17" s="242"/>
+      <x:c r="D17" s="242"/>
+      <x:c r="E17" s="242"/>
+      <x:c r="F17" s="242"/>
+      <x:c r="G17" s="242"/>
+      <x:c r="H17" s="245"/>
+      <x:c r="I17" s="246"/>
+      <x:c r="J17" s="217"/>
+      <x:c r="K17" s="252"/>
+      <x:c r="L17" s="254"/>
+    </x:row>
+    <x:row r="18" spans="1:12" ht="136.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <x:c r="A18" s="236"/>
+      <x:c r="B18" s="241"/>
+      <x:c r="C18" s="242"/>
+      <x:c r="D18" s="242"/>
+      <x:c r="E18" s="242"/>
+      <x:c r="F18" s="242"/>
+      <x:c r="G18" s="242"/>
+      <x:c r="H18" s="245"/>
+      <x:c r="I18" s="246"/>
+      <x:c r="J18" s="217"/>
+      <x:c r="K18" s="252"/>
+      <x:c r="L18" s="254"/>
+    </x:row>
+    <x:row r="19" spans="1:12" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <x:c r="A19" s="237"/>
+      <x:c r="B19" s="156" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="C19" s="157" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D19" s="158" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E19" s="157" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="F19" s="157" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G19" s="159" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H19" s="245"/>
+      <x:c r="I19" s="246"/>
+      <x:c r="J19" s="217"/>
+      <x:c r="K19" s="252"/>
+      <x:c r="L19" s="254"/>
+    </x:row>
+    <x:row r="20" spans="1:12" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <x:c r="A20" s="238"/>
+      <x:c r="B20" s="160"/>
+      <x:c r="C20" s="161"/>
+      <x:c r="D20" s="161"/>
+      <x:c r="E20" s="161"/>
+      <x:c r="F20" s="161"/>
+      <x:c r="G20" s="162"/>
+      <x:c r="H20" s="247"/>
+      <x:c r="I20" s="248"/>
+      <x:c r="J20" s="250"/>
+      <x:c r="K20" s="252"/>
+      <x:c r="L20" s="255"/>
+    </x:row>
+    <x:row r="21" spans="1:12" ht="12.4" customHeight="1" x14ac:dyDescent="0.3">
+      <x:c r="A21" s="194"/>
+      <x:c r="B21" s="197" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="C21" s="197"/>
+      <x:c r="D21" s="197"/>
+      <x:c r="E21" s="197"/>
+      <x:c r="F21" s="197"/>
+      <x:c r="G21" s="197"/>
+      <x:c r="H21" s="199"/>
+      <x:c r="I21" s="200"/>
+      <x:c r="J21" s="205" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K21" s="227">
+        <x:f>SUMPRODUCT(B26:G26,B25:G25)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L21" s="208">
+        <x:f>IF((K21-K28)&gt;=0,ROUND((K21-K28)*0.25,3),0.000000000001)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <x:c r="A22" s="195"/>
+      <x:c r="B22" s="198"/>
+      <x:c r="C22" s="198"/>
+      <x:c r="D22" s="198"/>
+      <x:c r="E22" s="198"/>
+      <x:c r="F22" s="198"/>
+      <x:c r="G22" s="198"/>
+      <x:c r="H22" s="201"/>
+      <x:c r="I22" s="202"/>
+      <x:c r="J22" s="206"/>
+      <x:c r="K22" s="228"/>
+      <x:c r="L22" s="209"/>
+    </x:row>
+    <x:row r="23" spans="1:12" ht="53" customHeight="1" x14ac:dyDescent="0.3">
+      <x:c r="A23" s="195"/>
+      <x:c r="B23" s="198"/>
+      <x:c r="C23" s="198"/>
+      <x:c r="D23" s="198"/>
+      <x:c r="E23" s="198"/>
+      <x:c r="F23" s="198"/>
+      <x:c r="G23" s="198"/>
+      <x:c r="H23" s="201"/>
+      <x:c r="I23" s="202"/>
+      <x:c r="J23" s="206"/>
+      <x:c r="K23" s="228"/>
+      <x:c r="L23" s="209"/>
+    </x:row>
+    <x:row r="24" spans="1:12" ht="15.4" customHeight="1" x14ac:dyDescent="0.3">
+      <x:c r="A24" s="195"/>
+      <x:c r="B24" s="219" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="C24" s="220"/>
+      <x:c r="D24" s="221" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="E24" s="222"/>
+      <x:c r="F24" s="223" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="G24" s="224"/>
+      <x:c r="H24" s="201"/>
+      <x:c r="I24" s="202"/>
+      <x:c r="J24" s="206"/>
+      <x:c r="K24" s="228"/>
+      <x:c r="L24" s="209"/>
+    </x:row>
+    <x:row r="25" spans="1:12" ht="13.9" customHeight="1" x14ac:dyDescent="0.3">
+      <x:c r="A25" s="195"/>
+      <x:c r="B25" s="225">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="C25" s="226"/>
+      <x:c r="D25" s="181">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="E25" s="182"/>
+      <x:c r="F25" s="183">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="G25" s="184"/>
+      <x:c r="H25" s="201"/>
+      <x:c r="I25" s="202"/>
+      <x:c r="J25" s="206"/>
+      <x:c r="K25" s="228"/>
+      <x:c r="L25" s="209"/>
+    </x:row>
+    <x:row r="26" spans="1:12" ht="28.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <x:c r="A26" s="195"/>
+      <x:c r="B26" s="185"/>
+      <x:c r="C26" s="186"/>
+      <x:c r="D26" s="187"/>
+      <x:c r="E26" s="188"/>
+      <x:c r="F26" s="186"/>
+      <x:c r="G26" s="189"/>
+      <x:c r="H26" s="201"/>
+      <x:c r="I26" s="202"/>
+      <x:c r="J26" s="206"/>
+      <x:c r="K26" s="229"/>
+      <x:c r="L26" s="209"/>
+    </x:row>
+    <x:row r="27" spans="1:12" ht="10.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <x:c r="A27" s="195"/>
+      <x:c r="B27" s="177"/>
+      <x:c r="C27" s="178"/>
+      <x:c r="D27" s="179"/>
+      <x:c r="E27" s="179"/>
+      <x:c r="F27" s="178"/>
+      <x:c r="G27" s="180"/>
+      <x:c r="H27" s="201"/>
+      <x:c r="I27" s="202"/>
+      <x:c r="J27" s="206"/>
+      <x:c r="K27" s="176"/>
+      <x:c r="L27" s="209"/>
+    </x:row>
+    <x:row r="28" spans="1:12" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <x:c r="A28" s="196"/>
+      <x:c r="B28" s="163" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="C28" s="164"/>
+      <x:c r="D28" s="164"/>
+      <x:c r="E28" s="164"/>
+      <x:c r="F28" s="164"/>
+      <x:c r="G28" s="164"/>
+      <x:c r="H28" s="203"/>
+      <x:c r="I28" s="204"/>
+      <x:c r="J28" s="207"/>
+      <x:c r="K28" s="165">
+        <x:f>SUM(C28:G28)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L28" s="210"/>
+    </x:row>
+    <x:row r="29" spans="1:12" ht="114.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <x:c r="A29" s="194" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B29" s="197" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C29" s="211"/>
+      <x:c r="D29" s="211"/>
+      <x:c r="E29" s="211"/>
+      <x:c r="F29" s="211"/>
+      <x:c r="G29" s="212"/>
+      <x:c r="H29" s="213"/>
+      <x:c r="I29" s="214"/>
+      <x:c r="J29" s="217" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="K29" s="166">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L29" s="190">
+        <x:f>IF((K29-K30)&gt;=0,ROUND((K29-K30)*0.15,3),0.00000000001)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:12" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <x:c r="A30" s="196"/>
+      <x:c r="B30" s="167" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="C30" s="164"/>
+      <x:c r="D30" s="164"/>
+      <x:c r="E30" s="164"/>
+      <x:c r="F30" s="164"/>
+      <x:c r="G30" s="164"/>
+      <x:c r="H30" s="215"/>
+      <x:c r="I30" s="216"/>
+      <x:c r="J30" s="218"/>
+      <x:c r="K30" s="165">
+        <x:f>SUM(C30:G30)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L30" s="191"/>
+    </x:row>
+    <x:row r="31" spans="1:12" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
+      <x:c r="A31" s="44"/>
+      <x:c r="B31" s="44"/>
+      <x:c r="C31" s="44"/>
+      <x:c r="D31" s="44"/>
+      <x:c r="E31" s="44"/>
+      <x:c r="F31" s="44"/>
+      <x:c r="G31" s="44"/>
+      <x:c r="H31" s="44"/>
+      <x:c r="K31" s="57"/>
+    </x:row>
+    <x:row r="32" spans="1:12" ht="28.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <x:c r="I32" s="45" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J32" s="46"/>
+      <x:c r="K32" s="192">
+        <x:f>SUM(L15:L29)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L32" s="193"/>
+    </x:row>
+    <x:row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <x:c r="A36" s="169" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B36" s="169"/>
+      <x:c r="C36" s="169"/>
+      <x:c r="D36" s="169"/>
+      <x:c r="E36" s="169"/>
+      <x:c r="F36" s="168"/>
+      <x:c r="G36" s="138"/>
+      <x:c r="H36" s="146" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I36" s="146"/>
+      <x:c r="J36" s="146"/>
+      <x:c r="K36" s="146"/>
+      <x:c r="L36" s="146"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells count="41">
+    <x:mergeCell ref="H12:K12"/>
+    <x:mergeCell ref="C4:D4"/>
+    <x:mergeCell ref="C5:E5"/>
+    <x:mergeCell ref="C6:E6"/>
+    <x:mergeCell ref="H7:K7"/>
+    <x:mergeCell ref="C8:E8"/>
+    <x:mergeCell ref="H8:K8"/>
+    <x:mergeCell ref="C9:E9"/>
+    <x:mergeCell ref="H9:K9"/>
+    <x:mergeCell ref="C10:E10"/>
+    <x:mergeCell ref="H10:K10"/>
+    <x:mergeCell ref="H11:K11"/>
+    <x:mergeCell ref="H14:I14"/>
+    <x:mergeCell ref="J14:L14"/>
+    <x:mergeCell ref="A15:A20"/>
+    <x:mergeCell ref="B15:G18"/>
+    <x:mergeCell ref="H15:I20"/>
+    <x:mergeCell ref="J15:J20"/>
+    <x:mergeCell ref="K15:K20"/>
+    <x:mergeCell ref="L15:L20"/>
+    <x:mergeCell ref="L29:L30"/>
+    <x:mergeCell ref="K32:L32"/>
+    <x:mergeCell ref="A21:A28"/>
+    <x:mergeCell ref="B21:G23"/>
+    <x:mergeCell ref="H21:I28"/>
+    <x:mergeCell ref="J21:J28"/>
+    <x:mergeCell ref="L21:L28"/>
+    <x:mergeCell ref="A29:A30"/>
+    <x:mergeCell ref="B29:G29"/>
+    <x:mergeCell ref="H29:I30"/>
+    <x:mergeCell ref="J29:J30"/>
+    <x:mergeCell ref="B24:C24"/>
+    <x:mergeCell ref="D24:E24"/>
+    <x:mergeCell ref="F24:G24"/>
+    <x:mergeCell ref="B25:C25"/>
+    <x:mergeCell ref="K21:K26"/>
+    <x:mergeCell ref="D25:E25"/>
+    <x:mergeCell ref="F25:G25"/>
+    <x:mergeCell ref="B26:C26"/>
+    <x:mergeCell ref="D26:E26"/>
+    <x:mergeCell ref="F26:G26"/>
+  </x:mergeCells>
+  <x:dataValidations count="1">
+    <x:dataValidation type="decimal" operator="lessThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Endast siffror giltiga" error="Ej giltig siffra_x000a_Kan du ha skrivit komma  istället för punkt eller tvärt om" sqref="C30:G30 C28 D28 E28 F28 G28 F26:G26 D26:E26 B26:C26 K29 B20 C20 D20 E20 F20 G20" xr:uid="{717696C7-3684-477B-A49A-9E6458A0FA01}">
+      <x:formula1>11</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.47244094488188981" right="0.15748031496062992" top="0.98425196850393704" bottom="0.39370078740157483" header="0.43307086614173229" footer="0.19685039370078741"/>
+  <x:pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId1"/>
+  <x:headerFooter alignWithMargins="0">
+    <x:oddHeader>&amp;L&amp;G
+&amp;C&amp;"Verdana,Normal"&amp;12PROTOKOLL FÖR LAGTÄVLAN</x:oddHeader>
+    <x:oddFooter>&amp;R2025-03-16</x:oddFooter>
+  </x:headerFooter>
+  <x:legacyDrawingHF r:id="rId2"/>
+</x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/mallar/Protokoll/Protokoll_2019_lag_sv-r_mellan(mall).xlsx
+++ b/mallar/Protokoll/Protokoll_2019_lag_sv-r_mellan(mall).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\episerver\voltige\VoltigeClosedXML\mallar\Protokoll\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\episerver\voltige\VoltigeClosedXML\voltexc\mallar\Protokoll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D54E0CEE-B78A-46E4-8FB4-DD51AEAB4E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF2E2B4-0BE0-44EE-83F6-73EDE6B1CCFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57855" yWindow="615" windowWidth="24315" windowHeight="19800" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Information" sheetId="27" r:id="rId1"/>
@@ -50,7 +50,7 @@
     <definedName name="datum" localSheetId="5">'Lag kür tekn mellan'!$C$4</definedName>
     <definedName name="datum" localSheetId="7">'Lag kür tekn sr'!$C$4</definedName>
     <definedName name="domare" localSheetId="1">'Häst, lag'!$C$36</definedName>
-    <definedName name="domare" localSheetId="2">'Lag grund A'!$C$33</definedName>
+    <definedName name="domare" localSheetId="2">'Lag grund A'!$C$32</definedName>
     <definedName name="domare" localSheetId="4">'Lag grund B'!$C$32</definedName>
     <definedName name="domare" localSheetId="3">'Lag grund D'!$C$33</definedName>
     <definedName name="domare" localSheetId="8">'Lag kür art'!$C$27</definedName>
@@ -96,7 +96,7 @@
     <definedName name="moment" localSheetId="5">'Lag kür tekn mellan'!$L$5</definedName>
     <definedName name="moment" localSheetId="7">'Lag kür tekn sr'!$L$5</definedName>
     <definedName name="result" localSheetId="1">'Häst, lag'!$K$32</definedName>
-    <definedName name="result" localSheetId="2">'Lag grund A'!$L$29</definedName>
+    <definedName name="result" localSheetId="2">'Lag grund A'!$L$28</definedName>
     <definedName name="result" localSheetId="4">'Lag grund B'!$L$29</definedName>
     <definedName name="result" localSheetId="3">'Lag grund D'!$L$29</definedName>
     <definedName name="result" localSheetId="8">'Lag kür art'!$L$24</definedName>
@@ -121,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="149">
   <si>
     <t>1)</t>
   </si>
@@ -238,9 +238,6 @@
     <t>Avdrag för fall</t>
   </si>
   <si>
-    <t>Sidhopp del 1</t>
-  </si>
-  <si>
     <t>Teknisk bedömning</t>
   </si>
   <si>
@@ -435,9 +432,6 @@
   </si>
   <si>
     <t>Sving baklänges, inkl avgång</t>
-  </si>
-  <si>
-    <t>Avhopp, utåt</t>
   </si>
   <si>
     <t>Lag grund D</t>
@@ -892,6 +886,12 @@
   </si>
   <si>
     <t>Lag kür senior</t>
+  </si>
+  <si>
+    <t>Sidhopp del 1, följt av avgång inåt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/ 7 övningar  </t>
   </si>
 </sst>
 </file>
@@ -1853,7 +1853,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="303">
+  <cellXfs count="306">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2328,257 +2328,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="9" fontId="25" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="25" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="52" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="61" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="62" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="53" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="55" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="46" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="47" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="48" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="52" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="53" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="47" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="52" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="25" fillId="0" borderId="59" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="50" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="51" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="46" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="52" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="53" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2606,6 +2355,266 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="25" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="25" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="60" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="52" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="61" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="62" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="53" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="55" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="46" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="47" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="48" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="52" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="53" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="47" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="52" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="57" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="58" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="25" fillId="0" borderId="59" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="50" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="51" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="46" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="52" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="53" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
@@ -2754,6 +2763,9 @@
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Information"/>
       <sheetName val="Häst, lag"/>
@@ -3070,109 +3082,109 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q60"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="18" width="15.73046875" customWidth="1"/>
+    <col min="1" max="18" width="15.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="125" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:8" s="125" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="124" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="125" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="125" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="125" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="125" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="125" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" s="125" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="125" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="137" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="137" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="137" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" s="137" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="137" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="137" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="137" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="1:8" s="125" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:8" s="111" customFormat="1" ht="17.25" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="137" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:8" s="125" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:8" s="111" customFormat="1" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A8" s="111" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="112"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="112"/>
+    </row>
+    <row r="12" spans="1:8" s="113" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A12" s="113" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="112"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="112"/>
-    </row>
-    <row r="12" spans="1:8" s="113" customFormat="1" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="A12" s="113" t="s">
+    <row r="13" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="114" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="114" t="s">
-        <v>66</v>
       </c>
       <c r="C13" s="112"/>
       <c r="F13" s="114" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="113" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="113" t="s">
+      <c r="C14" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="113" t="s">
+      <c r="D14" s="113" t="s">
         <v>69</v>
-      </c>
-      <c r="D14" s="113" t="s">
-        <v>70</v>
       </c>
       <c r="E14" s="113"/>
       <c r="F14" s="113" t="s">
+        <v>67</v>
+      </c>
+      <c r="G14" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="G14" s="113" t="s">
+      <c r="H14" s="113" t="s">
         <v>69</v>
       </c>
-      <c r="H14" s="113" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="112" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B15" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15" s="115" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D15" s="115" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E15" s="116"/>
       <c r="F15" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G15" s="115" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H15" s="115" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="112"/>
       <c r="B16" s="117"/>
       <c r="C16" s="117"/>
@@ -3182,31 +3194,31 @@
       <c r="G16" s="117"/>
       <c r="H16" s="117"/>
     </row>
-    <row r="17" spans="1:9" s="112" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" s="112" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="112" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B17" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C17" s="115" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D17" s="115" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E17" s="116"/>
       <c r="F17" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G17" s="115" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H17" s="115" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="112"/>
       <c r="B18" s="117"/>
       <c r="C18" s="117"/>
@@ -3216,31 +3228,31 @@
       <c r="G18" s="117"/>
       <c r="H18" s="117"/>
     </row>
-    <row r="19" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="112" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B19" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C19" s="115" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D19" s="115" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E19" s="116"/>
       <c r="F19" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G19" s="115" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H19" s="115" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="112"/>
       <c r="B20" s="118"/>
       <c r="C20" s="118"/>
@@ -3250,76 +3262,76 @@
       <c r="G20" s="118"/>
       <c r="H20" s="118"/>
     </row>
-    <row r="22" spans="1:9" s="113" customFormat="1" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:9" s="113" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A22" s="113" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="114" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C23" s="112"/>
       <c r="F23" s="114" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="113" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="113" t="s">
+      <c r="C24" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="113" t="s">
+      <c r="D24" s="113" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="113" t="s">
-        <v>70</v>
-      </c>
       <c r="E24" s="113" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F24" s="113" t="s">
+        <v>67</v>
+      </c>
+      <c r="G24" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="G24" s="113" t="s">
+      <c r="H24" s="113" t="s">
         <v>69</v>
       </c>
-      <c r="H24" s="113" t="s">
-        <v>70</v>
-      </c>
       <c r="I24" s="113" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="112" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B25" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C25" s="115" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D25" s="115" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E25" s="115" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F25" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G25" s="115" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H25" s="115" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I25" s="115" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="112"/>
       <c r="B26" s="117"/>
       <c r="C26" s="117"/>
@@ -3330,36 +3342,36 @@
       <c r="H26" s="117"/>
       <c r="I26" s="117"/>
     </row>
-    <row r="27" spans="1:9" s="112" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" s="112" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="112" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B27" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C27" s="115" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D27" s="115" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E27" s="115" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F27" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G27" s="115" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H27" s="115" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I27" s="115" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="112"/>
       <c r="B28" s="117"/>
       <c r="C28" s="117"/>
@@ -3370,134 +3382,134 @@
       <c r="H28" s="117"/>
       <c r="I28" s="117"/>
     </row>
-    <row r="29" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="112" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29" s="115" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="115" t="s">
+        <v>105</v>
+      </c>
+      <c r="D29" s="115" t="s">
+        <v>105</v>
+      </c>
+      <c r="E29" s="115" t="s">
+        <v>105</v>
+      </c>
+      <c r="F29" s="115" t="s">
+        <v>74</v>
+      </c>
+      <c r="G29" s="115" t="s">
+        <v>96</v>
+      </c>
+      <c r="H29" s="115" t="s">
         <v>78</v>
       </c>
-      <c r="B29" s="115" t="s">
-        <v>75</v>
-      </c>
-      <c r="C29" s="115" t="s">
-        <v>107</v>
-      </c>
-      <c r="D29" s="115" t="s">
-        <v>107</v>
-      </c>
-      <c r="E29" s="115" t="s">
-        <v>107</v>
-      </c>
-      <c r="F29" s="115" t="s">
-        <v>75</v>
-      </c>
-      <c r="G29" s="115" t="s">
-        <v>97</v>
-      </c>
-      <c r="H29" s="115" t="s">
-        <v>79</v>
-      </c>
       <c r="I29" s="115" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B30" s="136"/>
       <c r="C30" s="136"/>
       <c r="D30" s="136"/>
       <c r="E30" s="136"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B31" s="136"/>
       <c r="C31" s="136"/>
       <c r="D31" s="136"/>
       <c r="E31" s="136"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B32" s="136"/>
       <c r="C32" s="136"/>
       <c r="D32" s="136"/>
       <c r="E32" s="136"/>
     </row>
-    <row r="33" spans="1:17" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" ht="13" x14ac:dyDescent="0.3">
       <c r="A33" s="113" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="114" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C35" s="112"/>
       <c r="F35" s="114" t="s">
+        <v>66</v>
+      </c>
+      <c r="J35" s="114" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="113" t="s">
         <v>67</v>
       </c>
-      <c r="J35" s="114" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="113" t="s">
+      <c r="C36" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="C36" s="113" t="s">
+      <c r="D36" s="113" t="s">
         <v>69</v>
-      </c>
-      <c r="D36" s="113" t="s">
-        <v>70</v>
       </c>
       <c r="E36" s="113"/>
       <c r="F36" s="113" t="s">
+        <v>67</v>
+      </c>
+      <c r="G36" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="G36" s="113" t="s">
+      <c r="H36" s="113" t="s">
         <v>69</v>
       </c>
-      <c r="H36" s="113" t="s">
-        <v>70</v>
-      </c>
       <c r="J36" s="113" t="s">
+        <v>67</v>
+      </c>
+      <c r="K36" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="K36" s="113" t="s">
+      <c r="L36" s="113" t="s">
         <v>69</v>
       </c>
-      <c r="L36" s="113" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="112" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B37" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C37" s="115" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D37" s="115" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E37" s="116"/>
       <c r="F37" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G37" s="115" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H37" s="115" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J37" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K37" s="115" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L37" s="115" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="112"/>
       <c r="B38" s="117"/>
       <c r="C38" s="117"/>
@@ -3510,40 +3522,40 @@
       <c r="K38" s="117"/>
       <c r="L38" s="117"/>
     </row>
-    <row r="39" spans="1:17" s="112" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" s="112" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="112" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B39" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C39" s="115" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D39" s="115" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E39" s="116"/>
       <c r="F39" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G39" s="115" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H39" s="115" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J39" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K39" s="115" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L39" s="115" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="112"/>
       <c r="B40" s="117"/>
       <c r="C40" s="117"/>
@@ -3556,40 +3568,40 @@
       <c r="K40" s="117"/>
       <c r="L40" s="117"/>
     </row>
-    <row r="41" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="112" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B41" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C41" s="115" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D41" s="115" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E41" s="116"/>
       <c r="F41" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G41" s="115" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H41" s="115" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J41" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K41" s="115" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L41" s="115" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="112"/>
       <c r="B42" s="136"/>
       <c r="C42" s="136"/>
@@ -3602,7 +3614,7 @@
       <c r="K42" s="136"/>
       <c r="L42" s="136"/>
     </row>
-    <row r="43" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="112"/>
       <c r="B43" s="136"/>
       <c r="C43" s="136"/>
@@ -3615,109 +3627,109 @@
       <c r="K43" s="136"/>
       <c r="L43" s="136"/>
     </row>
-    <row r="45" spans="1:17" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" ht="13" x14ac:dyDescent="0.3">
       <c r="A45" s="113" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="114" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C47" s="112"/>
       <c r="F47" s="114" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J47" s="114" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K47" s="112"/>
       <c r="N47" s="114"/>
     </row>
-    <row r="48" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="113" t="s">
+        <v>67</v>
+      </c>
+      <c r="C48" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="C48" s="113" t="s">
+      <c r="D48" s="113" t="s">
         <v>69</v>
       </c>
-      <c r="D48" s="113" t="s">
-        <v>70</v>
-      </c>
       <c r="E48" s="113" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F48" s="113" t="s">
+        <v>67</v>
+      </c>
+      <c r="G48" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="G48" s="113" t="s">
+      <c r="H48" s="113" t="s">
         <v>69</v>
       </c>
-      <c r="H48" s="113" t="s">
-        <v>70</v>
-      </c>
       <c r="I48" s="113" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J48" s="113" t="s">
+        <v>67</v>
+      </c>
+      <c r="K48" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="K48" s="113" t="s">
+      <c r="L48" s="113" t="s">
         <v>69</v>
       </c>
-      <c r="L48" s="113" t="s">
-        <v>70</v>
-      </c>
       <c r="M48" s="113" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N48" s="113"/>
       <c r="O48" s="113"/>
       <c r="P48" s="113"/>
       <c r="Q48" s="113"/>
     </row>
-    <row r="49" spans="1:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:13" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="112" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B49" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C49" s="115" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D49" s="115" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E49" s="115" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F49" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G49" s="115" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H49" s="115" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I49" s="115" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J49" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K49" s="115" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L49" s="115" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M49" s="115" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="112"/>
       <c r="B50" s="117"/>
       <c r="C50" s="117"/>
@@ -3732,48 +3744,48 @@
       <c r="L50" s="117"/>
       <c r="M50" s="117"/>
     </row>
-    <row r="51" spans="1:13" s="112" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:13" s="112" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="112" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B51" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C51" s="115" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D51" s="115" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E51" s="115" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F51" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G51" s="115" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H51" s="115" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I51" s="115" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J51" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K51" s="115" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L51" s="115" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M51" s="115" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="112"/>
       <c r="B52" s="117"/>
       <c r="C52" s="117"/>
@@ -3788,118 +3800,118 @@
       <c r="L52" s="117"/>
       <c r="M52" s="117"/>
     </row>
-    <row r="53" spans="1:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:13" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="112" t="s">
+        <v>77</v>
+      </c>
+      <c r="B53" s="115" t="s">
+        <v>74</v>
+      </c>
+      <c r="C53" s="115" t="s">
+        <v>105</v>
+      </c>
+      <c r="D53" s="115" t="s">
+        <v>105</v>
+      </c>
+      <c r="E53" s="115" t="s">
+        <v>105</v>
+      </c>
+      <c r="F53" s="115" t="s">
+        <v>74</v>
+      </c>
+      <c r="G53" s="115" t="s">
+        <v>96</v>
+      </c>
+      <c r="H53" s="115" t="s">
         <v>78</v>
       </c>
-      <c r="B53" s="115" t="s">
-        <v>75</v>
-      </c>
-      <c r="C53" s="115" t="s">
-        <v>107</v>
-      </c>
-      <c r="D53" s="115" t="s">
-        <v>107</v>
-      </c>
-      <c r="E53" s="115" t="s">
-        <v>107</v>
-      </c>
-      <c r="F53" s="115" t="s">
-        <v>75</v>
-      </c>
-      <c r="G53" s="115" t="s">
-        <v>97</v>
-      </c>
-      <c r="H53" s="115" t="s">
-        <v>79</v>
-      </c>
       <c r="I53" s="115" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J53" s="115" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K53" s="115" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L53" s="115" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M53" s="115" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" s="125" customFormat="1" ht="17.25" x14ac:dyDescent="0.45">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" s="125" customFormat="1" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A56" s="123" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" s="122" customFormat="1" ht="13.15" x14ac:dyDescent="0.4">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" s="122" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A57" s="121"/>
       <c r="B57" s="121" t="s">
+        <v>67</v>
+      </c>
+      <c r="C57" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="C57" s="121" t="s">
+      <c r="D57" s="121" t="s">
         <v>69</v>
       </c>
-      <c r="D57" s="121" t="s">
-        <v>70</v>
-      </c>
       <c r="E57" s="121" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F57" s="121" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" s="120" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="119" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="58" spans="1:13" s="120" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="119" t="s">
+      <c r="B58" s="119" t="s">
         <v>84</v>
       </c>
-      <c r="B58" s="119" t="s">
+      <c r="C58" s="119" t="s">
         <v>85</v>
       </c>
-      <c r="C58" s="119" t="s">
+      <c r="D58" s="119" t="s">
+        <v>85</v>
+      </c>
+      <c r="E58" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="D58" s="119" t="s">
-        <v>86</v>
-      </c>
-      <c r="E58" s="119" t="s">
+      <c r="F58" s="119" t="s">
         <v>87</v>
       </c>
-      <c r="F58" s="119" t="s">
+    </row>
+    <row r="59" spans="1:13" s="120" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="119" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="59" spans="1:13" s="120" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="119" t="s">
+      <c r="B59" s="119" t="s">
+        <v>84</v>
+      </c>
+      <c r="C59" s="119" t="s">
         <v>89</v>
       </c>
-      <c r="B59" s="119" t="s">
-        <v>85</v>
-      </c>
-      <c r="C59" s="119" t="s">
+      <c r="D59" s="119" t="s">
         <v>90</v>
       </c>
-      <c r="D59" s="119" t="s">
+      <c r="E59" s="119" t="s">
         <v>91</v>
       </c>
-      <c r="E59" s="119" t="s">
-        <v>92</v>
-      </c>
       <c r="F59" s="119" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" s="120" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" s="120" customFormat="1" ht="25" x14ac:dyDescent="0.25">
       <c r="A60" s="119"/>
       <c r="B60" s="119"/>
       <c r="C60" s="119"/>
       <c r="D60" s="119"/>
       <c r="E60" s="119"/>
       <c r="F60" s="119" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -3920,30 +3932,30 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="12.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1328125" style="1"/>
-    <col min="3" max="3" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="1" customWidth="1"/>
-    <col min="5" max="7" width="7.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.36328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.08984375" style="1"/>
+    <col min="3" max="3" width="12.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.7265625" style="1" customWidth="1"/>
+    <col min="5" max="7" width="7.26953125" style="1" customWidth="1"/>
     <col min="8" max="8" width="7" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.265625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="4.73046875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.265625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.73046875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7.265625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.1328125" style="1"/>
+    <col min="9" max="9" width="7.26953125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="4.7265625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.26953125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7265625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.26953125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:13" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="11"/>
@@ -3951,11 +3963,11 @@
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J3" s="10"/>
       <c r="K3" s="11"/>
@@ -3972,7 +3984,7 @@
       <c r="F4" s="8"/>
       <c r="H4" s="9"/>
       <c r="I4" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J4" s="10"/>
       <c r="K4" s="11"/>
@@ -3983,10 +3995,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="12"/>
-      <c r="C5" s="261"/>
-      <c r="D5" s="261"/>
-      <c r="E5" s="261"/>
-      <c r="F5" s="261"/>
+      <c r="C5" s="181"/>
+      <c r="D5" s="181"/>
+      <c r="E5" s="181"/>
+      <c r="F5" s="181"/>
       <c r="H5" s="9"/>
       <c r="I5" s="13" t="s">
         <v>10</v>
@@ -4000,17 +4012,17 @@
         <v>13</v>
       </c>
       <c r="B6" s="12"/>
-      <c r="C6" s="261"/>
-      <c r="D6" s="261"/>
-      <c r="E6" s="261"/>
-      <c r="F6" s="261"/>
+      <c r="C6" s="181"/>
+      <c r="D6" s="181"/>
+      <c r="E6" s="181"/>
+      <c r="F6" s="181"/>
       <c r="H6" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="70"/>
@@ -4020,80 +4032,80 @@
       <c r="H7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I7" s="266"/>
-      <c r="J7" s="267"/>
-      <c r="K7" s="267"/>
-      <c r="L7" s="268"/>
-    </row>
-    <row r="8" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="186"/>
+      <c r="J7" s="187"/>
+      <c r="K7" s="187"/>
+      <c r="L7" s="188"/>
+    </row>
+    <row r="8" spans="1:13" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="266"/>
-      <c r="D8" s="266"/>
-      <c r="E8" s="266"/>
-      <c r="F8" s="266"/>
+      <c r="C8" s="186"/>
+      <c r="D8" s="186"/>
+      <c r="E8" s="186"/>
+      <c r="F8" s="186"/>
       <c r="H8" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="I8" s="261"/>
-      <c r="J8" s="262"/>
-      <c r="K8" s="262"/>
-      <c r="L8" s="263"/>
-    </row>
-    <row r="9" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I8" s="181"/>
+      <c r="J8" s="182"/>
+      <c r="K8" s="182"/>
+      <c r="L8" s="183"/>
+    </row>
+    <row r="9" spans="1:13" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="12"/>
-      <c r="C9" s="261"/>
-      <c r="D9" s="261"/>
-      <c r="E9" s="261"/>
-      <c r="F9" s="261"/>
+      <c r="C9" s="181"/>
+      <c r="D9" s="181"/>
+      <c r="E9" s="181"/>
+      <c r="F9" s="181"/>
       <c r="H9" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="I9" s="261"/>
-      <c r="J9" s="262"/>
-      <c r="K9" s="262"/>
-      <c r="L9" s="263"/>
-    </row>
-    <row r="10" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I9" s="181"/>
+      <c r="J9" s="182"/>
+      <c r="K9" s="182"/>
+      <c r="L9" s="183"/>
+    </row>
+    <row r="10" spans="1:13" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B10" s="12"/>
-      <c r="C10" s="261"/>
-      <c r="D10" s="261"/>
-      <c r="E10" s="261"/>
-      <c r="F10" s="261"/>
+      <c r="C10" s="181"/>
+      <c r="D10" s="181"/>
+      <c r="E10" s="181"/>
+      <c r="F10" s="181"/>
       <c r="H10" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="I10" s="261"/>
-      <c r="J10" s="262"/>
-      <c r="K10" s="262"/>
-      <c r="L10" s="263"/>
-    </row>
-    <row r="11" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I10" s="181"/>
+      <c r="J10" s="182"/>
+      <c r="K10" s="182"/>
+      <c r="L10" s="183"/>
+    </row>
+    <row r="11" spans="1:13" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H11" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="I11" s="261"/>
-      <c r="J11" s="262"/>
-      <c r="K11" s="262"/>
-      <c r="L11" s="263"/>
-    </row>
-    <row r="12" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I11" s="181"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="182"/>
+      <c r="L11" s="183"/>
+    </row>
+    <row r="12" spans="1:13" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="14"/>
       <c r="H12" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="I12" s="261"/>
-      <c r="J12" s="262"/>
-      <c r="K12" s="262"/>
-      <c r="L12" s="263"/>
+      <c r="I12" s="181"/>
+      <c r="J12" s="182"/>
+      <c r="K12" s="182"/>
+      <c r="L12" s="183"/>
     </row>
     <row r="13" spans="1:13" ht="8.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="14"/>
@@ -4107,25 +4119,25 @@
       <c r="C14" s="14"/>
       <c r="I14" s="66"/>
       <c r="K14" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="172" t="s">
+        <v>125</v>
+      </c>
+      <c r="B15" s="291" t="s">
+        <v>126</v>
+      </c>
+      <c r="C15" s="292"/>
+      <c r="D15" s="292"/>
+      <c r="E15" s="292"/>
+      <c r="F15" s="292"/>
+      <c r="G15" s="292"/>
+      <c r="H15" s="292"/>
+      <c r="I15" s="293"/>
+      <c r="J15" s="173" t="s">
         <v>127</v>
-      </c>
-      <c r="B15" s="288" t="s">
-        <v>128</v>
-      </c>
-      <c r="C15" s="289"/>
-      <c r="D15" s="289"/>
-      <c r="E15" s="289"/>
-      <c r="F15" s="289"/>
-      <c r="G15" s="289"/>
-      <c r="H15" s="289"/>
-      <c r="I15" s="290"/>
-      <c r="J15" s="173" t="s">
-        <v>129</v>
       </c>
       <c r="K15" s="174"/>
       <c r="L15" s="175">
@@ -4134,21 +4146,21 @@
       </c>
     </row>
     <row r="16" spans="1:13" ht="66.400000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="291" t="s">
-        <v>143</v>
-      </c>
-      <c r="B16" s="295" t="s">
+      <c r="A16" s="294" t="s">
         <v>141</v>
       </c>
-      <c r="C16" s="296"/>
-      <c r="D16" s="296"/>
-      <c r="E16" s="296"/>
-      <c r="F16" s="296"/>
-      <c r="G16" s="296"/>
-      <c r="H16" s="296"/>
-      <c r="I16" s="296"/>
+      <c r="B16" s="298" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="299"/>
+      <c r="D16" s="299"/>
+      <c r="E16" s="299"/>
+      <c r="F16" s="299"/>
+      <c r="G16" s="299"/>
+      <c r="H16" s="299"/>
+      <c r="I16" s="299"/>
       <c r="J16" s="78" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K16" s="130"/>
       <c r="L16" s="79">
@@ -4158,19 +4170,19 @@
       <c r="M16" s="80"/>
     </row>
     <row r="17" spans="1:13" ht="83.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="292"/>
-      <c r="B17" s="295" t="s">
-        <v>142</v>
-      </c>
-      <c r="C17" s="296"/>
-      <c r="D17" s="296"/>
-      <c r="E17" s="296"/>
-      <c r="F17" s="296"/>
-      <c r="G17" s="296"/>
-      <c r="H17" s="296"/>
-      <c r="I17" s="296"/>
+      <c r="A17" s="295"/>
+      <c r="B17" s="298" t="s">
+        <v>140</v>
+      </c>
+      <c r="C17" s="299"/>
+      <c r="D17" s="299"/>
+      <c r="E17" s="299"/>
+      <c r="F17" s="299"/>
+      <c r="G17" s="299"/>
+      <c r="H17" s="299"/>
+      <c r="I17" s="299"/>
       <c r="J17" s="81" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K17" s="131"/>
       <c r="L17" s="82">
@@ -4180,21 +4192,21 @@
       <c r="M17" s="80"/>
     </row>
     <row r="18" spans="1:13" ht="58.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="293" t="s">
-        <v>144</v>
-      </c>
-      <c r="B18" s="297" t="s">
-        <v>131</v>
-      </c>
-      <c r="C18" s="298"/>
-      <c r="D18" s="298"/>
-      <c r="E18" s="298"/>
-      <c r="F18" s="298"/>
-      <c r="G18" s="298"/>
-      <c r="H18" s="298"/>
-      <c r="I18" s="299"/>
+      <c r="A18" s="296" t="s">
+        <v>142</v>
+      </c>
+      <c r="B18" s="300" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="301"/>
+      <c r="D18" s="301"/>
+      <c r="E18" s="301"/>
+      <c r="F18" s="301"/>
+      <c r="G18" s="301"/>
+      <c r="H18" s="301"/>
+      <c r="I18" s="302"/>
       <c r="J18" s="78" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K18" s="132"/>
       <c r="L18" s="83">
@@ -4204,19 +4216,19 @@
       <c r="M18" s="80"/>
     </row>
     <row r="19" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="294"/>
-      <c r="B19" s="300" t="s">
-        <v>132</v>
-      </c>
-      <c r="C19" s="301"/>
-      <c r="D19" s="301"/>
-      <c r="E19" s="301"/>
-      <c r="F19" s="301"/>
-      <c r="G19" s="301"/>
-      <c r="H19" s="301"/>
-      <c r="I19" s="302"/>
+      <c r="A19" s="297"/>
+      <c r="B19" s="303" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" s="304"/>
+      <c r="D19" s="304"/>
+      <c r="E19" s="304"/>
+      <c r="F19" s="304"/>
+      <c r="G19" s="304"/>
+      <c r="H19" s="304"/>
+      <c r="I19" s="305"/>
       <c r="J19" s="84" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="K19" s="133"/>
       <c r="L19" s="85">
@@ -4239,7 +4251,7 @@
     </row>
     <row r="22" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="47" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22" s="61"/>
       <c r="D22" s="48"/>
@@ -4257,7 +4269,7 @@
     </row>
     <row r="24" spans="1:13" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I24" s="49" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J24" s="76"/>
       <c r="K24" s="76"/>
@@ -4302,13 +4314,13 @@
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="B16:I16"/>
     <mergeCell ref="B17:I17"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="I9:L9"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="I7:L7"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="I8:L8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="I9:L9"/>
   </mergeCells>
   <pageMargins left="0.78740157480314965" right="0.15748031496062992" top="0.98425196850393704" bottom="0.39370078740157483" header="0.43307086614173229" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4327,70 +4339,70 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L36"/>
-  <sheetFormatPr defaultColWidth="9.06640625" defaultRowHeight="12.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.73046875" style="43" customWidth="1"/>
-    <col min="2" max="2" width="8.796875" style="43" customWidth="1"/>
-    <col min="3" max="3" width="10.265625" style="43" customWidth="1"/>
-    <col min="4" max="4" width="10.06640625" style="43" customWidth="1"/>
-    <col min="5" max="5" width="9.796875" style="43" customWidth="1"/>
-    <col min="6" max="7" width="9.9296875" style="43" customWidth="1"/>
-    <col min="8" max="8" width="6.265625" style="43" customWidth="1"/>
-    <col min="9" max="9" width="5.73046875" style="43" customWidth="1"/>
-    <col min="10" max="11" width="7.06640625" style="43" customWidth="1"/>
-    <col min="12" max="12" width="7.265625" style="43" customWidth="1"/>
-    <col min="13" max="16384" width="9.06640625" style="43"/>
+    <col min="1" max="1" width="5.7265625" style="43" customWidth="1"/>
+    <col min="2" max="2" width="8.81640625" style="43" customWidth="1"/>
+    <col min="3" max="3" width="10.26953125" style="43" customWidth="1"/>
+    <col min="4" max="4" width="10.08984375" style="43" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" style="43" customWidth="1"/>
+    <col min="6" max="7" width="9.90625" style="43" customWidth="1"/>
+    <col min="8" max="8" width="6.26953125" style="43" customWidth="1"/>
+    <col min="9" max="9" width="5.7265625" style="43" customWidth="1"/>
+    <col min="10" max="11" width="7.08984375" style="43" customWidth="1"/>
+    <col min="12" max="12" width="7.26953125" style="43" customWidth="1"/>
+    <col min="13" max="16384" width="9.08984375" style="43"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="138" customFormat="1" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:12" s="138" customFormat="1" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" s="138" customFormat="1" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="139" t="s">
         <v>8</v>
       </c>
       <c r="G2" s="140"/>
       <c r="H2" s="141" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I2" s="142"/>
       <c r="J2" s="143"/>
       <c r="K2" s="144"/>
     </row>
-    <row r="3" spans="1:12" s="138" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" s="138" customFormat="1" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="145" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="140"/>
       <c r="H3" s="141" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I3" s="142"/>
       <c r="J3" s="143"/>
       <c r="K3" s="144"/>
     </row>
-    <row r="4" spans="1:12" s="138" customFormat="1" ht="17.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" s="138" customFormat="1" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="146" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="146"/>
-      <c r="C4" s="258"/>
-      <c r="D4" s="258"/>
+      <c r="C4" s="273"/>
+      <c r="D4" s="273"/>
       <c r="E4" s="147"/>
       <c r="G4" s="140"/>
       <c r="H4" s="141" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I4" s="142"/>
       <c r="J4" s="143"/>
       <c r="K4" s="144"/>
     </row>
-    <row r="5" spans="1:12" s="138" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" s="138" customFormat="1" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="148" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="148"/>
-      <c r="C5" s="256"/>
-      <c r="D5" s="256"/>
-      <c r="E5" s="256"/>
+      <c r="C5" s="271"/>
+      <c r="D5" s="271"/>
+      <c r="E5" s="271"/>
       <c r="G5" s="140"/>
       <c r="H5" s="141" t="s">
         <v>10</v>
@@ -4404,17 +4416,17 @@
         <v>13</v>
       </c>
       <c r="B6" s="148"/>
-      <c r="C6" s="256"/>
-      <c r="D6" s="256"/>
-      <c r="E6" s="256"/>
+      <c r="C6" s="271"/>
+      <c r="D6" s="271"/>
+      <c r="E6" s="271"/>
       <c r="G6" s="138" t="s">
         <v>15</v>
       </c>
       <c r="K6" s="150"/>
     </row>
-    <row r="7" spans="1:12" s="138" customFormat="1" ht="17.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" s="138" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="148" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B7" s="148"/>
       <c r="C7" s="151"/>
@@ -4423,77 +4435,77 @@
       <c r="G7" s="146" t="s">
         <v>0</v>
       </c>
-      <c r="H7" s="259"/>
-      <c r="I7" s="260"/>
-      <c r="J7" s="260"/>
-      <c r="K7" s="260"/>
-    </row>
-    <row r="8" spans="1:12" s="138" customFormat="1" ht="17.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H7" s="274"/>
+      <c r="I7" s="275"/>
+      <c r="J7" s="275"/>
+      <c r="K7" s="275"/>
+    </row>
+    <row r="8" spans="1:12" s="138" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="146" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="146"/>
-      <c r="C8" s="259"/>
-      <c r="D8" s="259"/>
-      <c r="E8" s="259"/>
+      <c r="C8" s="274"/>
+      <c r="D8" s="274"/>
+      <c r="E8" s="274"/>
       <c r="G8" s="148" t="s">
         <v>1</v>
       </c>
-      <c r="H8" s="256"/>
-      <c r="I8" s="257"/>
-      <c r="J8" s="257"/>
-      <c r="K8" s="257"/>
-    </row>
-    <row r="9" spans="1:12" s="138" customFormat="1" ht="17.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H8" s="271"/>
+      <c r="I8" s="272"/>
+      <c r="J8" s="272"/>
+      <c r="K8" s="272"/>
+    </row>
+    <row r="9" spans="1:12" s="138" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="148" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="148"/>
-      <c r="C9" s="256"/>
-      <c r="D9" s="256"/>
-      <c r="E9" s="256"/>
+      <c r="C9" s="271"/>
+      <c r="D9" s="271"/>
+      <c r="E9" s="271"/>
       <c r="G9" s="148" t="s">
         <v>2</v>
       </c>
-      <c r="H9" s="256"/>
-      <c r="I9" s="257"/>
-      <c r="J9" s="257"/>
-      <c r="K9" s="257"/>
-    </row>
-    <row r="10" spans="1:12" s="138" customFormat="1" ht="17.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H9" s="271"/>
+      <c r="I9" s="272"/>
+      <c r="J9" s="272"/>
+      <c r="K9" s="272"/>
+    </row>
+    <row r="10" spans="1:12" s="138" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="148" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B10" s="148"/>
-      <c r="C10" s="256"/>
-      <c r="D10" s="256"/>
-      <c r="E10" s="256"/>
+      <c r="C10" s="271"/>
+      <c r="D10" s="271"/>
+      <c r="E10" s="271"/>
       <c r="G10" s="148" t="s">
         <v>3</v>
       </c>
-      <c r="H10" s="256"/>
-      <c r="I10" s="257"/>
-      <c r="J10" s="257"/>
-      <c r="K10" s="257"/>
-    </row>
-    <row r="11" spans="1:12" s="138" customFormat="1" ht="17.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H10" s="271"/>
+      <c r="I10" s="272"/>
+      <c r="J10" s="272"/>
+      <c r="K10" s="272"/>
+    </row>
+    <row r="11" spans="1:12" s="138" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G11" s="148" t="s">
         <v>4</v>
       </c>
-      <c r="H11" s="256"/>
-      <c r="I11" s="257"/>
-      <c r="J11" s="257"/>
-      <c r="K11" s="257"/>
-    </row>
-    <row r="12" spans="1:12" s="138" customFormat="1" ht="17.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H11" s="271"/>
+      <c r="I11" s="272"/>
+      <c r="J11" s="272"/>
+      <c r="K11" s="272"/>
+    </row>
+    <row r="12" spans="1:12" s="138" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="152"/>
       <c r="G12" s="148" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="256"/>
-      <c r="I12" s="257"/>
-      <c r="J12" s="257"/>
-      <c r="K12" s="257"/>
+      <c r="H12" s="271"/>
+      <c r="I12" s="272"/>
+      <c r="J12" s="272"/>
+      <c r="K12" s="272"/>
     </row>
     <row r="13" spans="1:12" s="138" customFormat="1" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C13" s="152"/>
@@ -4503,7 +4515,7 @@
       <c r="J13" s="153"/>
       <c r="K13" s="153"/>
     </row>
-    <row r="14" spans="1:12" ht="12.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" ht="14" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="138"/>
       <c r="B14" s="138"/>
       <c r="C14" s="155"/>
@@ -4511,308 +4523,308 @@
       <c r="E14" s="155"/>
       <c r="F14" s="155"/>
       <c r="G14" s="138"/>
-      <c r="H14" s="230" t="s">
+      <c r="H14" s="245" t="s">
         <v>26</v>
       </c>
-      <c r="I14" s="231"/>
-      <c r="J14" s="232" t="s">
-        <v>60</v>
-      </c>
-      <c r="K14" s="233"/>
-      <c r="L14" s="234"/>
+      <c r="I14" s="246"/>
+      <c r="J14" s="247" t="s">
+        <v>59</v>
+      </c>
+      <c r="K14" s="248"/>
+      <c r="L14" s="249"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="235" t="s">
+      <c r="A15" s="250" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15" s="254" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" s="255"/>
+      <c r="D15" s="255"/>
+      <c r="E15" s="255"/>
+      <c r="F15" s="255"/>
+      <c r="G15" s="255"/>
+      <c r="H15" s="258"/>
+      <c r="I15" s="259"/>
+      <c r="J15" s="264" t="s">
         <v>113</v>
       </c>
-      <c r="B15" s="239" t="s">
+      <c r="K15" s="266">
+        <f>SUM(B20:G20)/6</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="268">
+        <f>ROUND(K15*0.6,3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="251"/>
+      <c r="B16" s="256"/>
+      <c r="C16" s="257"/>
+      <c r="D16" s="257"/>
+      <c r="E16" s="257"/>
+      <c r="F16" s="257"/>
+      <c r="G16" s="257"/>
+      <c r="H16" s="260"/>
+      <c r="I16" s="261"/>
+      <c r="J16" s="232"/>
+      <c r="K16" s="267"/>
+      <c r="L16" s="269"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="251"/>
+      <c r="B17" s="256"/>
+      <c r="C17" s="257"/>
+      <c r="D17" s="257"/>
+      <c r="E17" s="257"/>
+      <c r="F17" s="257"/>
+      <c r="G17" s="257"/>
+      <c r="H17" s="260"/>
+      <c r="I17" s="261"/>
+      <c r="J17" s="232"/>
+      <c r="K17" s="267"/>
+      <c r="L17" s="269"/>
+    </row>
+    <row r="18" spans="1:12" ht="136.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="251"/>
+      <c r="B18" s="256"/>
+      <c r="C18" s="257"/>
+      <c r="D18" s="257"/>
+      <c r="E18" s="257"/>
+      <c r="F18" s="257"/>
+      <c r="G18" s="257"/>
+      <c r="H18" s="260"/>
+      <c r="I18" s="261"/>
+      <c r="J18" s="232"/>
+      <c r="K18" s="267"/>
+      <c r="L18" s="269"/>
+    </row>
+    <row r="19" spans="1:12" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="252"/>
+      <c r="B19" s="156" t="s">
         <v>114</v>
       </c>
-      <c r="C15" s="240"/>
-      <c r="D15" s="240"/>
-      <c r="E15" s="240"/>
-      <c r="F15" s="240"/>
-      <c r="G15" s="240"/>
-      <c r="H15" s="243"/>
-      <c r="I15" s="244"/>
-      <c r="J15" s="249" t="s">
+      <c r="C19" s="157" t="s">
         <v>115</v>
       </c>
-      <c r="K15" s="251">
-        <f>SUM(B20:G20)/6</f>
-        <v>0</v>
-      </c>
-      <c r="L15" s="253">
-        <f>ROUND(K15*0.6,3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="236"/>
-      <c r="B16" s="241"/>
-      <c r="C16" s="242"/>
-      <c r="D16" s="242"/>
-      <c r="E16" s="242"/>
-      <c r="F16" s="242"/>
-      <c r="G16" s="242"/>
-      <c r="H16" s="245"/>
-      <c r="I16" s="246"/>
-      <c r="J16" s="217"/>
-      <c r="K16" s="252"/>
-      <c r="L16" s="254"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="236"/>
-      <c r="B17" s="241"/>
-      <c r="C17" s="242"/>
-      <c r="D17" s="242"/>
-      <c r="E17" s="242"/>
-      <c r="F17" s="242"/>
-      <c r="G17" s="242"/>
-      <c r="H17" s="245"/>
-      <c r="I17" s="246"/>
-      <c r="J17" s="217"/>
-      <c r="K17" s="252"/>
-      <c r="L17" s="254"/>
-    </row>
-    <row r="18" spans="1:12" ht="136.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="236"/>
-      <c r="B18" s="241"/>
-      <c r="C18" s="242"/>
-      <c r="D18" s="242"/>
-      <c r="E18" s="242"/>
-      <c r="F18" s="242"/>
-      <c r="G18" s="242"/>
-      <c r="H18" s="245"/>
-      <c r="I18" s="246"/>
-      <c r="J18" s="217"/>
-      <c r="K18" s="252"/>
-      <c r="L18" s="254"/>
-    </row>
-    <row r="19" spans="1:12" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="237"/>
-      <c r="B19" s="156" t="s">
+      <c r="D19" s="158" t="s">
         <v>116</v>
       </c>
-      <c r="C19" s="157" t="s">
+      <c r="E19" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="D19" s="158" t="s">
+      <c r="F19" s="157" t="s">
         <v>118</v>
       </c>
-      <c r="E19" s="157" t="s">
+      <c r="G19" s="159" t="s">
         <v>119</v>
       </c>
-      <c r="F19" s="157" t="s">
-        <v>120</v>
-      </c>
-      <c r="G19" s="159" t="s">
-        <v>121</v>
-      </c>
-      <c r="H19" s="245"/>
-      <c r="I19" s="246"/>
-      <c r="J19" s="217"/>
-      <c r="K19" s="252"/>
-      <c r="L19" s="254"/>
-    </row>
-    <row r="20" spans="1:12" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="238"/>
+      <c r="H19" s="260"/>
+      <c r="I19" s="261"/>
+      <c r="J19" s="232"/>
+      <c r="K19" s="267"/>
+      <c r="L19" s="269"/>
+    </row>
+    <row r="20" spans="1:12" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="253"/>
       <c r="B20" s="160"/>
       <c r="C20" s="161"/>
       <c r="D20" s="161"/>
       <c r="E20" s="161"/>
       <c r="F20" s="161"/>
       <c r="G20" s="162"/>
-      <c r="H20" s="247"/>
-      <c r="I20" s="248"/>
-      <c r="J20" s="250"/>
-      <c r="K20" s="252"/>
-      <c r="L20" s="255"/>
+      <c r="H20" s="262"/>
+      <c r="I20" s="263"/>
+      <c r="J20" s="265"/>
+      <c r="K20" s="267"/>
+      <c r="L20" s="270"/>
     </row>
     <row r="21" spans="1:12" ht="12.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="194"/>
-      <c r="B21" s="197" t="s">
-        <v>136</v>
-      </c>
-      <c r="C21" s="197"/>
-      <c r="D21" s="197"/>
-      <c r="E21" s="197"/>
-      <c r="F21" s="197"/>
-      <c r="G21" s="197"/>
-      <c r="H21" s="199"/>
-      <c r="I21" s="200"/>
-      <c r="J21" s="205" t="s">
+      <c r="A21" s="209"/>
+      <c r="B21" s="212" t="s">
+        <v>134</v>
+      </c>
+      <c r="C21" s="212"/>
+      <c r="D21" s="212"/>
+      <c r="E21" s="212"/>
+      <c r="F21" s="212"/>
+      <c r="G21" s="212"/>
+      <c r="H21" s="214"/>
+      <c r="I21" s="215"/>
+      <c r="J21" s="220" t="s">
         <v>7</v>
       </c>
-      <c r="K21" s="227">
+      <c r="K21" s="242">
         <f>SUMPRODUCT(B26:G26,B25:G25)</f>
         <v>0</v>
       </c>
-      <c r="L21" s="208">
+      <c r="L21" s="223">
         <f>IF((K21-K28)&gt;=0,ROUND((K21-K28)*0.25,3),0.000000000001)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="195"/>
-      <c r="B22" s="198"/>
-      <c r="C22" s="198"/>
-      <c r="D22" s="198"/>
-      <c r="E22" s="198"/>
-      <c r="F22" s="198"/>
-      <c r="G22" s="198"/>
-      <c r="H22" s="201"/>
-      <c r="I22" s="202"/>
-      <c r="J22" s="206"/>
-      <c r="K22" s="228"/>
-      <c r="L22" s="209"/>
+      <c r="A22" s="210"/>
+      <c r="B22" s="213"/>
+      <c r="C22" s="213"/>
+      <c r="D22" s="213"/>
+      <c r="E22" s="213"/>
+      <c r="F22" s="213"/>
+      <c r="G22" s="213"/>
+      <c r="H22" s="216"/>
+      <c r="I22" s="217"/>
+      <c r="J22" s="221"/>
+      <c r="K22" s="243"/>
+      <c r="L22" s="224"/>
     </row>
     <row r="23" spans="1:12" ht="53" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="195"/>
-      <c r="B23" s="198"/>
-      <c r="C23" s="198"/>
-      <c r="D23" s="198"/>
-      <c r="E23" s="198"/>
-      <c r="F23" s="198"/>
-      <c r="G23" s="198"/>
-      <c r="H23" s="201"/>
-      <c r="I23" s="202"/>
-      <c r="J23" s="206"/>
-      <c r="K23" s="228"/>
-      <c r="L23" s="209"/>
+      <c r="A23" s="210"/>
+      <c r="B23" s="213"/>
+      <c r="C23" s="213"/>
+      <c r="D23" s="213"/>
+      <c r="E23" s="213"/>
+      <c r="F23" s="213"/>
+      <c r="G23" s="213"/>
+      <c r="H23" s="216"/>
+      <c r="I23" s="217"/>
+      <c r="J23" s="221"/>
+      <c r="K23" s="243"/>
+      <c r="L23" s="224"/>
     </row>
     <row r="24" spans="1:12" ht="15.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="195"/>
-      <c r="B24" s="219" t="s">
+      <c r="A24" s="210"/>
+      <c r="B24" s="234" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="235"/>
+      <c r="D24" s="236" t="s">
+        <v>132</v>
+      </c>
+      <c r="E24" s="237"/>
+      <c r="F24" s="238" t="s">
         <v>133</v>
       </c>
-      <c r="C24" s="220"/>
-      <c r="D24" s="221" t="s">
-        <v>134</v>
-      </c>
-      <c r="E24" s="222"/>
-      <c r="F24" s="223" t="s">
-        <v>135</v>
-      </c>
-      <c r="G24" s="224"/>
-      <c r="H24" s="201"/>
-      <c r="I24" s="202"/>
-      <c r="J24" s="206"/>
-      <c r="K24" s="228"/>
-      <c r="L24" s="209"/>
+      <c r="G24" s="239"/>
+      <c r="H24" s="216"/>
+      <c r="I24" s="217"/>
+      <c r="J24" s="221"/>
+      <c r="K24" s="243"/>
+      <c r="L24" s="224"/>
     </row>
     <row r="25" spans="1:12" ht="13.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="195"/>
-      <c r="B25" s="225">
+      <c r="A25" s="210"/>
+      <c r="B25" s="240">
         <v>0.5</v>
       </c>
-      <c r="C25" s="226"/>
-      <c r="D25" s="181">
+      <c r="C25" s="241"/>
+      <c r="D25" s="196">
         <v>0.25</v>
       </c>
-      <c r="E25" s="182"/>
-      <c r="F25" s="183">
+      <c r="E25" s="197"/>
+      <c r="F25" s="198">
         <v>0.25</v>
       </c>
-      <c r="G25" s="184"/>
-      <c r="H25" s="201"/>
-      <c r="I25" s="202"/>
-      <c r="J25" s="206"/>
-      <c r="K25" s="228"/>
-      <c r="L25" s="209"/>
+      <c r="G25" s="199"/>
+      <c r="H25" s="216"/>
+      <c r="I25" s="217"/>
+      <c r="J25" s="221"/>
+      <c r="K25" s="243"/>
+      <c r="L25" s="224"/>
     </row>
     <row r="26" spans="1:12" ht="28.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="195"/>
-      <c r="B26" s="185"/>
-      <c r="C26" s="186"/>
-      <c r="D26" s="187"/>
-      <c r="E26" s="188"/>
-      <c r="F26" s="186"/>
-      <c r="G26" s="189"/>
-      <c r="H26" s="201"/>
-      <c r="I26" s="202"/>
-      <c r="J26" s="206"/>
-      <c r="K26" s="229"/>
-      <c r="L26" s="209"/>
+      <c r="A26" s="210"/>
+      <c r="B26" s="200"/>
+      <c r="C26" s="201"/>
+      <c r="D26" s="202"/>
+      <c r="E26" s="203"/>
+      <c r="F26" s="201"/>
+      <c r="G26" s="204"/>
+      <c r="H26" s="216"/>
+      <c r="I26" s="217"/>
+      <c r="J26" s="221"/>
+      <c r="K26" s="244"/>
+      <c r="L26" s="224"/>
     </row>
     <row r="27" spans="1:12" ht="10.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="195"/>
+      <c r="A27" s="210"/>
       <c r="B27" s="177"/>
       <c r="C27" s="178"/>
       <c r="D27" s="179"/>
       <c r="E27" s="179"/>
       <c r="F27" s="178"/>
       <c r="G27" s="180"/>
-      <c r="H27" s="201"/>
-      <c r="I27" s="202"/>
-      <c r="J27" s="206"/>
+      <c r="H27" s="216"/>
+      <c r="I27" s="217"/>
+      <c r="J27" s="221"/>
       <c r="K27" s="176"/>
-      <c r="L27" s="209"/>
-    </row>
-    <row r="28" spans="1:12" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="196"/>
+      <c r="L27" s="224"/>
+    </row>
+    <row r="28" spans="1:12" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="211"/>
       <c r="B28" s="163" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C28" s="164"/>
       <c r="D28" s="164"/>
       <c r="E28" s="164"/>
       <c r="F28" s="164"/>
       <c r="G28" s="164"/>
-      <c r="H28" s="203"/>
-      <c r="I28" s="204"/>
-      <c r="J28" s="207"/>
+      <c r="H28" s="218"/>
+      <c r="I28" s="219"/>
+      <c r="J28" s="222"/>
       <c r="K28" s="165">
         <f>SUM(C28:G28)</f>
         <v>0</v>
       </c>
-      <c r="L28" s="210"/>
+      <c r="L28" s="225"/>
     </row>
     <row r="29" spans="1:12" ht="114.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="194" t="s">
+      <c r="A29" s="209" t="s">
         <v>16</v>
       </c>
-      <c r="B29" s="197" t="s">
-        <v>137</v>
-      </c>
-      <c r="C29" s="211"/>
-      <c r="D29" s="211"/>
-      <c r="E29" s="211"/>
-      <c r="F29" s="211"/>
-      <c r="G29" s="212"/>
-      <c r="H29" s="213"/>
-      <c r="I29" s="214"/>
-      <c r="J29" s="217" t="s">
-        <v>123</v>
+      <c r="B29" s="212" t="s">
+        <v>135</v>
+      </c>
+      <c r="C29" s="226"/>
+      <c r="D29" s="226"/>
+      <c r="E29" s="226"/>
+      <c r="F29" s="226"/>
+      <c r="G29" s="227"/>
+      <c r="H29" s="228"/>
+      <c r="I29" s="229"/>
+      <c r="J29" s="232" t="s">
+        <v>121</v>
       </c>
       <c r="K29" s="166">
         <v>0</v>
       </c>
-      <c r="L29" s="190">
+      <c r="L29" s="205">
         <f>IF((K29-K30)&gt;=0,ROUND((K29-K30)*0.15,3),0.00000000001)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="28.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="196"/>
+    <row r="30" spans="1:12" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="211"/>
       <c r="B30" s="167" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C30" s="164"/>
       <c r="D30" s="164"/>
       <c r="E30" s="164"/>
       <c r="F30" s="164"/>
       <c r="G30" s="164"/>
-      <c r="H30" s="215"/>
-      <c r="I30" s="216"/>
-      <c r="J30" s="218"/>
+      <c r="H30" s="230"/>
+      <c r="I30" s="231"/>
+      <c r="J30" s="233"/>
       <c r="K30" s="165">
         <f>SUM(C30:G30)</f>
         <v>0</v>
       </c>
-      <c r="L30" s="191"/>
-    </row>
-    <row r="31" spans="1:12" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L30" s="206"/>
+    </row>
+    <row r="31" spans="1:12" ht="14" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="44"/>
       <c r="B31" s="44"/>
       <c r="C31" s="44"/>
@@ -4828,11 +4840,11 @@
         <v>9</v>
       </c>
       <c r="J32" s="46"/>
-      <c r="K32" s="192">
+      <c r="K32" s="207">
         <f>SUM(L15:L29)</f>
         <v>0</v>
       </c>
-      <c r="L32" s="193"/>
+      <c r="L32" s="208"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="169" t="s">
@@ -4914,29 +4926,29 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="12.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L34"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1328125" style="1"/>
-    <col min="3" max="3" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="1" customWidth="1"/>
-    <col min="5" max="7" width="7.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.08984375" style="1"/>
+    <col min="3" max="3" width="12.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.7265625" style="1" customWidth="1"/>
+    <col min="5" max="7" width="7.26953125" style="1" customWidth="1"/>
     <col min="8" max="8" width="7" style="1" customWidth="1"/>
-    <col min="9" max="11" width="7.265625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.59765625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7.265625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.1328125" style="1"/>
+    <col min="9" max="11" width="7.26953125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6328125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.26953125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="11"/>
@@ -4944,11 +4956,11 @@
     </row>
     <row r="3" spans="1:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J3" s="10"/>
       <c r="K3" s="11"/>
@@ -4965,7 +4977,7 @@
       <c r="F4" s="8"/>
       <c r="H4" s="9"/>
       <c r="I4" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J4" s="10"/>
       <c r="K4" s="11"/>
@@ -4976,10 +4988,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="12"/>
-      <c r="C5" s="261"/>
-      <c r="D5" s="261"/>
-      <c r="E5" s="261"/>
-      <c r="F5" s="261"/>
+      <c r="C5" s="181"/>
+      <c r="D5" s="181"/>
+      <c r="E5" s="181"/>
+      <c r="F5" s="181"/>
       <c r="H5" s="9"/>
       <c r="I5" s="13" t="s">
         <v>10</v>
@@ -4993,17 +5005,17 @@
         <v>13</v>
       </c>
       <c r="B6" s="12"/>
-      <c r="C6" s="261"/>
-      <c r="D6" s="261"/>
-      <c r="E6" s="261"/>
-      <c r="F6" s="261"/>
+      <c r="C6" s="181"/>
+      <c r="D6" s="181"/>
+      <c r="E6" s="181"/>
+      <c r="F6" s="181"/>
       <c r="H6" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="70"/>
@@ -5013,79 +5025,79 @@
       <c r="H7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I7" s="266"/>
-      <c r="J7" s="267"/>
-      <c r="K7" s="267"/>
-      <c r="L7" s="268"/>
-    </row>
-    <row r="8" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="186"/>
+      <c r="J7" s="187"/>
+      <c r="K7" s="187"/>
+      <c r="L7" s="188"/>
+    </row>
+    <row r="8" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="266"/>
-      <c r="D8" s="266"/>
-      <c r="E8" s="266"/>
-      <c r="F8" s="266"/>
+      <c r="C8" s="186"/>
+      <c r="D8" s="186"/>
+      <c r="E8" s="186"/>
+      <c r="F8" s="186"/>
       <c r="H8" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="I8" s="261"/>
-      <c r="J8" s="262"/>
-      <c r="K8" s="262"/>
-      <c r="L8" s="263"/>
-    </row>
-    <row r="9" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I8" s="181"/>
+      <c r="J8" s="182"/>
+      <c r="K8" s="182"/>
+      <c r="L8" s="183"/>
+    </row>
+    <row r="9" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="12"/>
-      <c r="C9" s="261"/>
-      <c r="D9" s="261"/>
-      <c r="E9" s="261"/>
-      <c r="F9" s="261"/>
+      <c r="C9" s="181"/>
+      <c r="D9" s="181"/>
+      <c r="E9" s="181"/>
+      <c r="F9" s="181"/>
       <c r="H9" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="I9" s="261"/>
-      <c r="J9" s="262"/>
-      <c r="K9" s="262"/>
-      <c r="L9" s="263"/>
-    </row>
-    <row r="10" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I9" s="181"/>
+      <c r="J9" s="182"/>
+      <c r="K9" s="182"/>
+      <c r="L9" s="183"/>
+    </row>
+    <row r="10" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B10" s="12"/>
-      <c r="C10" s="261"/>
-      <c r="D10" s="261"/>
-      <c r="E10" s="261"/>
-      <c r="F10" s="261"/>
+      <c r="C10" s="181"/>
+      <c r="D10" s="181"/>
+      <c r="E10" s="181"/>
+      <c r="F10" s="181"/>
       <c r="H10" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="I10" s="261"/>
-      <c r="J10" s="262"/>
-      <c r="K10" s="262"/>
-      <c r="L10" s="263"/>
-    </row>
-    <row r="11" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I10" s="181"/>
+      <c r="J10" s="182"/>
+      <c r="K10" s="182"/>
+      <c r="L10" s="183"/>
+    </row>
+    <row r="11" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H11" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="I11" s="261"/>
-      <c r="J11" s="262"/>
-      <c r="K11" s="262"/>
-      <c r="L11" s="263"/>
-    </row>
-    <row r="12" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I11" s="181"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="182"/>
+      <c r="L11" s="183"/>
+    </row>
+    <row r="12" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H12" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="I12" s="261"/>
-      <c r="J12" s="262"/>
-      <c r="K12" s="262"/>
-      <c r="L12" s="263"/>
+      <c r="I12" s="181"/>
+      <c r="J12" s="182"/>
+      <c r="K12" s="182"/>
+      <c r="L12" s="183"/>
     </row>
     <row r="13" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="15"/>
@@ -5114,218 +5126,292 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="271"/>
-      <c r="B15" s="272" t="s">
+    <row r="15" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="191"/>
+      <c r="B15" s="192" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="265"/>
-      <c r="D15" s="265"/>
+      <c r="C15" s="185"/>
+      <c r="D15" s="185"/>
       <c r="E15" s="18"/>
-      <c r="F15" s="127"/>
-      <c r="G15" s="127"/>
-      <c r="H15" s="127"/>
-      <c r="I15" s="127"/>
-      <c r="J15" s="127"/>
-      <c r="K15" s="127"/>
+      <c r="F15" s="127">
+        <v>0</v>
+      </c>
+      <c r="G15" s="127">
+        <v>0</v>
+      </c>
+      <c r="H15" s="127">
+        <v>0</v>
+      </c>
+      <c r="I15" s="127">
+        <v>0</v>
+      </c>
+      <c r="J15" s="127">
+        <v>0</v>
+      </c>
+      <c r="K15" s="127">
+        <v>0</v>
+      </c>
       <c r="L15" s="19">
         <f>SUM(F15:K15)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="271"/>
-      <c r="B16" s="264" t="s">
+    <row r="16" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="191"/>
+      <c r="B16" s="184" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="265"/>
-      <c r="D16" s="265"/>
+      <c r="C16" s="185"/>
+      <c r="D16" s="185"/>
       <c r="E16" s="18"/>
-      <c r="F16" s="127"/>
-      <c r="G16" s="127"/>
-      <c r="H16" s="127"/>
-      <c r="I16" s="127"/>
-      <c r="J16" s="127"/>
-      <c r="K16" s="127"/>
+      <c r="F16" s="127">
+        <v>0</v>
+      </c>
+      <c r="G16" s="127">
+        <v>0</v>
+      </c>
+      <c r="H16" s="127">
+        <v>0</v>
+      </c>
+      <c r="I16" s="127">
+        <v>0</v>
+      </c>
+      <c r="J16" s="127">
+        <v>0</v>
+      </c>
+      <c r="K16" s="127">
+        <v>0</v>
+      </c>
       <c r="L16" s="19">
-        <f t="shared" ref="L16:L22" si="0">SUM(F16:K16)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="264" t="s">
+        <f t="shared" ref="L16:L21" si="0">SUM(F16:K16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="184" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="265"/>
-      <c r="D17" s="265"/>
+      <c r="C17" s="185"/>
+      <c r="D17" s="185"/>
       <c r="E17" s="18"/>
-      <c r="F17" s="127"/>
-      <c r="G17" s="127"/>
-      <c r="H17" s="127"/>
-      <c r="I17" s="127"/>
-      <c r="J17" s="127"/>
-      <c r="K17" s="127"/>
+      <c r="F17" s="127">
+        <v>0</v>
+      </c>
+      <c r="G17" s="127">
+        <v>0</v>
+      </c>
+      <c r="H17" s="127">
+        <v>0</v>
+      </c>
+      <c r="I17" s="127">
+        <v>0</v>
+      </c>
+      <c r="J17" s="127">
+        <v>0</v>
+      </c>
+      <c r="K17" s="127">
+        <v>0</v>
+      </c>
       <c r="L17" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="269" t="s">
+    <row r="18" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="189" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="270"/>
-      <c r="D18" s="270"/>
+      <c r="C18" s="190"/>
+      <c r="D18" s="190"/>
       <c r="E18" s="18"/>
-      <c r="F18" s="127"/>
-      <c r="G18" s="127"/>
-      <c r="H18" s="127"/>
-      <c r="I18" s="127"/>
-      <c r="J18" s="127"/>
-      <c r="K18" s="127"/>
+      <c r="F18" s="127">
+        <v>0</v>
+      </c>
+      <c r="G18" s="127">
+        <v>0</v>
+      </c>
+      <c r="H18" s="127">
+        <v>0</v>
+      </c>
+      <c r="I18" s="127">
+        <v>0</v>
+      </c>
+      <c r="J18" s="127">
+        <v>0</v>
+      </c>
+      <c r="K18" s="127">
+        <v>0</v>
+      </c>
       <c r="L18" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="264" t="s">
+    <row r="19" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="184" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="265"/>
-      <c r="D19" s="265"/>
+      <c r="C19" s="185"/>
+      <c r="D19" s="185"/>
       <c r="E19" s="20"/>
-      <c r="F19" s="127"/>
-      <c r="G19" s="127"/>
-      <c r="H19" s="127"/>
-      <c r="I19" s="127"/>
-      <c r="J19" s="127"/>
-      <c r="K19" s="127"/>
+      <c r="F19" s="127">
+        <v>0</v>
+      </c>
+      <c r="G19" s="127">
+        <v>0</v>
+      </c>
+      <c r="H19" s="127">
+        <v>0</v>
+      </c>
+      <c r="I19" s="127">
+        <v>0</v>
+      </c>
+      <c r="J19" s="127">
+        <v>0</v>
+      </c>
+      <c r="K19" s="127">
+        <v>0</v>
+      </c>
       <c r="L19" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="47" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="48"/>
       <c r="D20" s="48"/>
       <c r="E20" s="18"/>
-      <c r="F20" s="127"/>
-      <c r="G20" s="127"/>
-      <c r="H20" s="127"/>
-      <c r="I20" s="127"/>
-      <c r="J20" s="127"/>
-      <c r="K20" s="127"/>
+      <c r="F20" s="127">
+        <v>0</v>
+      </c>
+      <c r="G20" s="127">
+        <v>0</v>
+      </c>
+      <c r="H20" s="127">
+        <v>0</v>
+      </c>
+      <c r="I20" s="127">
+        <v>0</v>
+      </c>
+      <c r="J20" s="127">
+        <v>0</v>
+      </c>
+      <c r="K20" s="127">
+        <v>0</v>
+      </c>
       <c r="L20" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" s="48"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="127"/>
-      <c r="G21" s="127"/>
-      <c r="H21" s="127"/>
-      <c r="I21" s="127"/>
-      <c r="J21" s="127"/>
-      <c r="K21" s="127"/>
+    <row r="21" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="193" t="s">
+        <v>147</v>
+      </c>
+      <c r="C21" s="194"/>
+      <c r="D21" s="194"/>
+      <c r="E21" s="195"/>
+      <c r="F21" s="127">
+        <v>0</v>
+      </c>
+      <c r="G21" s="127">
+        <v>0</v>
+      </c>
+      <c r="H21" s="127">
+        <v>0</v>
+      </c>
+      <c r="I21" s="127">
+        <v>0</v>
+      </c>
+      <c r="J21" s="127">
+        <v>0</v>
+      </c>
+      <c r="K21" s="127">
+        <v>0</v>
+      </c>
       <c r="L21" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="273" t="s">
-        <v>104</v>
-      </c>
-      <c r="C22" s="274"/>
-      <c r="D22" s="274"/>
-      <c r="E22" s="275"/>
-      <c r="F22" s="127"/>
-      <c r="G22" s="127"/>
-      <c r="H22" s="127"/>
-      <c r="I22" s="127"/>
-      <c r="J22" s="127"/>
-      <c r="K22" s="127"/>
-      <c r="L22" s="19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="2:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="22" t="s">
+    <row r="22" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="23"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="23"/>
+      <c r="K23" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="L23" s="19">
+        <f>SUM(L15:L21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="25"/>
+      <c r="H24" s="26"/>
+      <c r="J24" s="24"/>
       <c r="K24" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="L24" s="19">
-        <f>SUM(L15:L22)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>34</v>
+      </c>
+      <c r="L24" s="27">
+        <f>ROUND(+L23/6,3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B25" s="25"/>
       <c r="H25" s="26"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="L25" s="27">
-        <f>ROUND(+L24/6,3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B26" s="25"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="29"/>
-      <c r="L26" s="30"/>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B27" s="31"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="32"/>
-      <c r="K27" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="L27" s="29"/>
-    </row>
-    <row r="28" spans="2:12" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="2:12" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I25" s="28"/>
+      <c r="J25" s="29"/>
+      <c r="L25" s="30"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B26" s="31"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="32"/>
+      <c r="K26" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="L26" s="29"/>
+    </row>
+    <row r="27" spans="1:12" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="28" spans="1:12" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F28" s="38"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="J28" s="50"/>
+      <c r="K28" s="51"/>
+      <c r="L28" s="37">
+        <f>ROUND(+L24/7,3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F29" s="38"/>
       <c r="H29" s="33"/>
-      <c r="I29" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="J29" s="50"/>
-      <c r="K29" s="51"/>
-      <c r="L29" s="37">
-        <f>ROUND(+L25/8,3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I29" s="33"/>
+      <c r="J29" s="39"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="6"/>
+    </row>
+    <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F30" s="38"/>
       <c r="H30" s="33"/>
       <c r="I30" s="33"/>
@@ -5333,42 +5419,34 @@
       <c r="K30" s="24"/>
       <c r="L30" s="6"/>
     </row>
-    <row r="31" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F31" s="38"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="33"/>
-      <c r="J31" s="39"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="6"/>
-    </row>
-    <row r="32" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" s="40"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="38"/>
+      <c r="H32" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+    </row>
     <row r="33" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B33" s="40"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="40"/>
       <c r="F33" s="38"/>
-      <c r="H33" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-    </row>
-    <row r="34" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F34" s="38"/>
-      <c r="H34" s="33"/>
-      <c r="I34" s="33"/>
-      <c r="J34" s="39"/>
-      <c r="K34" s="24"/>
-      <c r="L34" s="6"/>
-    </row>
-    <row r="35" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="41"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="39"/>
+      <c r="K33" s="24"/>
+      <c r="L33" s="6"/>
+    </row>
+    <row r="34" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -5376,7 +5454,7 @@
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B21:E21"/>
     <mergeCell ref="I12:L12"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="C8:F8"/>
@@ -5396,7 +5474,7 @@
   <headerFooter alignWithMargins="0">
     <oddHeader>&amp;L&amp;G
 &amp;C&amp;"Verdana,Normal"&amp;12PROTOKOLL FÖR LAGTÄVLAN</oddHeader>
-    <oddFooter xml:space="preserve">&amp;R2019-06-01
+    <oddFooter xml:space="preserve">&amp;R2026-01-25
 </oddFooter>
   </headerFooter>
   <legacyDrawingHF r:id="rId2"/>
@@ -5406,28 +5484,28 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M66"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="12.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1328125" style="1"/>
-    <col min="3" max="3" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="1" customWidth="1"/>
-    <col min="5" max="7" width="7.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.08984375" style="1"/>
+    <col min="3" max="3" width="12.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.7265625" style="1" customWidth="1"/>
+    <col min="5" max="7" width="7.26953125" style="1" customWidth="1"/>
     <col min="8" max="8" width="7" style="1" customWidth="1"/>
-    <col min="9" max="11" width="7.265625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.59765625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7.265625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.1328125" style="1"/>
+    <col min="9" max="11" width="7.26953125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6328125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.26953125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="11"/>
@@ -5435,11 +5513,11 @@
     </row>
     <row r="3" spans="1:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J3" s="10"/>
       <c r="K3" s="11"/>
@@ -5456,7 +5534,7 @@
       <c r="F4" s="8"/>
       <c r="H4" s="9"/>
       <c r="I4" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J4" s="10"/>
       <c r="K4" s="11"/>
@@ -5467,10 +5545,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="12"/>
-      <c r="C5" s="261"/>
-      <c r="D5" s="261"/>
-      <c r="E5" s="261"/>
-      <c r="F5" s="261"/>
+      <c r="C5" s="181"/>
+      <c r="D5" s="181"/>
+      <c r="E5" s="181"/>
+      <c r="F5" s="181"/>
       <c r="H5" s="9"/>
       <c r="I5" s="13" t="s">
         <v>10</v>
@@ -5484,17 +5562,17 @@
         <v>13</v>
       </c>
       <c r="B6" s="12"/>
-      <c r="C6" s="261"/>
-      <c r="D6" s="261"/>
-      <c r="E6" s="261"/>
-      <c r="F6" s="261"/>
+      <c r="C6" s="181"/>
+      <c r="D6" s="181"/>
+      <c r="E6" s="181"/>
+      <c r="F6" s="181"/>
       <c r="H6" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="70"/>
@@ -5504,82 +5582,82 @@
       <c r="H7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I7" s="266"/>
-      <c r="J7" s="267"/>
-      <c r="K7" s="267"/>
-      <c r="L7" s="267"/>
-    </row>
-    <row r="8" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="186"/>
+      <c r="J7" s="187"/>
+      <c r="K7" s="187"/>
+      <c r="L7" s="187"/>
+    </row>
+    <row r="8" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="266"/>
-      <c r="D8" s="266"/>
-      <c r="E8" s="266"/>
-      <c r="F8" s="266"/>
+      <c r="C8" s="186"/>
+      <c r="D8" s="186"/>
+      <c r="E8" s="186"/>
+      <c r="F8" s="186"/>
       <c r="H8" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="I8" s="261"/>
-      <c r="J8" s="262"/>
-      <c r="K8" s="262"/>
-      <c r="L8" s="262"/>
-    </row>
-    <row r="9" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I8" s="181"/>
+      <c r="J8" s="182"/>
+      <c r="K8" s="182"/>
+      <c r="L8" s="182"/>
+    </row>
+    <row r="9" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="12"/>
-      <c r="C9" s="261"/>
-      <c r="D9" s="261"/>
-      <c r="E9" s="261"/>
-      <c r="F9" s="261"/>
+      <c r="C9" s="181"/>
+      <c r="D9" s="181"/>
+      <c r="E9" s="181"/>
+      <c r="F9" s="181"/>
       <c r="H9" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="I9" s="261"/>
-      <c r="J9" s="262"/>
-      <c r="K9" s="262"/>
-      <c r="L9" s="262"/>
-    </row>
-    <row r="10" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I9" s="181"/>
+      <c r="J9" s="182"/>
+      <c r="K9" s="182"/>
+      <c r="L9" s="182"/>
+    </row>
+    <row r="10" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B10" s="12"/>
-      <c r="C10" s="261"/>
-      <c r="D10" s="261"/>
-      <c r="E10" s="261"/>
-      <c r="F10" s="261"/>
+      <c r="C10" s="181"/>
+      <c r="D10" s="181"/>
+      <c r="E10" s="181"/>
+      <c r="F10" s="181"/>
       <c r="H10" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="I10" s="261"/>
-      <c r="J10" s="262"/>
-      <c r="K10" s="262"/>
-      <c r="L10" s="262"/>
-    </row>
-    <row r="11" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I10" s="181"/>
+      <c r="J10" s="182"/>
+      <c r="K10" s="182"/>
+      <c r="L10" s="182"/>
+    </row>
+    <row r="11" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H11" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="I11" s="261"/>
-      <c r="J11" s="262"/>
-      <c r="K11" s="262"/>
-      <c r="L11" s="262"/>
-    </row>
-    <row r="12" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I11" s="181"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="182"/>
+      <c r="L11" s="182"/>
+    </row>
+    <row r="12" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="14"/>
       <c r="H12" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="I12" s="261"/>
-      <c r="J12" s="262"/>
-      <c r="K12" s="262"/>
-      <c r="L12" s="262"/>
-    </row>
-    <row r="13" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I12" s="181"/>
+      <c r="J12" s="182"/>
+      <c r="K12" s="182"/>
+      <c r="L12" s="182"/>
+    </row>
+    <row r="13" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
@@ -5613,13 +5691,13 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="271"/>
-      <c r="B16" s="272" t="s">
+    <row r="16" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="191"/>
+      <c r="B16" s="192" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="265"/>
-      <c r="D16" s="265"/>
+      <c r="C16" s="185"/>
+      <c r="D16" s="185"/>
       <c r="E16" s="18"/>
       <c r="F16" s="127"/>
       <c r="G16" s="127"/>
@@ -5632,13 +5710,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="271"/>
-      <c r="B17" s="264" t="s">
+    <row r="17" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="191"/>
+      <c r="B17" s="184" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="265"/>
-      <c r="D17" s="265"/>
+      <c r="C17" s="185"/>
+      <c r="D17" s="185"/>
       <c r="E17" s="18"/>
       <c r="F17" s="127"/>
       <c r="G17" s="127"/>
@@ -5651,12 +5729,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="264" t="s">
+    <row r="18" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="184" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="265"/>
-      <c r="D18" s="265"/>
+      <c r="C18" s="185"/>
+      <c r="D18" s="185"/>
       <c r="E18" s="18"/>
       <c r="F18" s="127"/>
       <c r="G18" s="127"/>
@@ -5669,12 +5747,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="276" t="s">
+    <row r="19" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="279" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="265"/>
-      <c r="D19" s="265"/>
+      <c r="C19" s="185"/>
+      <c r="D19" s="185"/>
       <c r="E19" s="18"/>
       <c r="F19" s="127"/>
       <c r="G19" s="127"/>
@@ -5687,13 +5765,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="264" t="s">
-        <v>102</v>
-      </c>
-      <c r="C20" s="265"/>
-      <c r="D20" s="265"/>
-      <c r="E20" s="277"/>
+    <row r="20" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="184" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20" s="185"/>
+      <c r="D20" s="185"/>
+      <c r="E20" s="280"/>
       <c r="F20" s="127"/>
       <c r="G20" s="127"/>
       <c r="H20" s="127"/>
@@ -5705,12 +5783,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="264" t="s">
+    <row r="21" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="184" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="265"/>
-      <c r="D21" s="265"/>
+      <c r="C21" s="185"/>
+      <c r="D21" s="185"/>
       <c r="E21" s="18"/>
       <c r="F21" s="127"/>
       <c r="G21" s="127"/>
@@ -5723,13 +5801,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="273" t="s">
-        <v>103</v>
-      </c>
-      <c r="C22" s="274"/>
-      <c r="D22" s="274"/>
-      <c r="E22" s="275"/>
+    <row r="22" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="276" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" s="277"/>
+      <c r="D22" s="277"/>
+      <c r="E22" s="278"/>
       <c r="F22" s="127"/>
       <c r="G22" s="127"/>
       <c r="H22" s="127"/>
@@ -5920,28 +5998,28 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L34"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="12.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1328125" style="1"/>
-    <col min="3" max="3" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="1" customWidth="1"/>
-    <col min="5" max="7" width="7.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.08984375" style="1"/>
+    <col min="3" max="3" width="12.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.7265625" style="1" customWidth="1"/>
+    <col min="5" max="7" width="7.26953125" style="1" customWidth="1"/>
     <col min="8" max="8" width="7" style="1" customWidth="1"/>
-    <col min="9" max="11" width="7.265625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.59765625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7.265625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.1328125" style="1"/>
+    <col min="9" max="11" width="7.26953125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6328125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.26953125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="11"/>
@@ -5949,11 +6027,11 @@
     </row>
     <row r="3" spans="1:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J3" s="10"/>
       <c r="K3" s="11"/>
@@ -5970,7 +6048,7 @@
       <c r="F4" s="8"/>
       <c r="H4" s="9"/>
       <c r="I4" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J4" s="10"/>
       <c r="K4" s="11"/>
@@ -5981,10 +6059,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="12"/>
-      <c r="C5" s="261"/>
-      <c r="D5" s="261"/>
-      <c r="E5" s="261"/>
-      <c r="F5" s="261"/>
+      <c r="C5" s="181"/>
+      <c r="D5" s="181"/>
+      <c r="E5" s="181"/>
+      <c r="F5" s="181"/>
       <c r="H5" s="9"/>
       <c r="I5" s="13" t="s">
         <v>10</v>
@@ -5998,17 +6076,17 @@
         <v>13</v>
       </c>
       <c r="B6" s="12"/>
-      <c r="C6" s="261"/>
-      <c r="D6" s="261"/>
-      <c r="E6" s="261"/>
-      <c r="F6" s="261"/>
+      <c r="C6" s="181"/>
+      <c r="D6" s="181"/>
+      <c r="E6" s="181"/>
+      <c r="F6" s="181"/>
       <c r="H6" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="70"/>
@@ -6018,80 +6096,80 @@
       <c r="H7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I7" s="266"/>
-      <c r="J7" s="267"/>
-      <c r="K7" s="267"/>
-      <c r="L7" s="268"/>
-    </row>
-    <row r="8" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="186"/>
+      <c r="J7" s="187"/>
+      <c r="K7" s="187"/>
+      <c r="L7" s="188"/>
+    </row>
+    <row r="8" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="266"/>
-      <c r="D8" s="266"/>
-      <c r="E8" s="266"/>
-      <c r="F8" s="266"/>
+      <c r="C8" s="186"/>
+      <c r="D8" s="186"/>
+      <c r="E8" s="186"/>
+      <c r="F8" s="186"/>
       <c r="H8" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="I8" s="261"/>
-      <c r="J8" s="262"/>
-      <c r="K8" s="262"/>
-      <c r="L8" s="263"/>
-    </row>
-    <row r="9" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I8" s="181"/>
+      <c r="J8" s="182"/>
+      <c r="K8" s="182"/>
+      <c r="L8" s="183"/>
+    </row>
+    <row r="9" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="12"/>
-      <c r="C9" s="261"/>
-      <c r="D9" s="261"/>
-      <c r="E9" s="261"/>
-      <c r="F9" s="261"/>
+      <c r="C9" s="181"/>
+      <c r="D9" s="181"/>
+      <c r="E9" s="181"/>
+      <c r="F9" s="181"/>
       <c r="H9" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="I9" s="261"/>
-      <c r="J9" s="262"/>
-      <c r="K9" s="262"/>
-      <c r="L9" s="263"/>
-    </row>
-    <row r="10" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I9" s="181"/>
+      <c r="J9" s="182"/>
+      <c r="K9" s="182"/>
+      <c r="L9" s="183"/>
+    </row>
+    <row r="10" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B10" s="12"/>
-      <c r="C10" s="261"/>
-      <c r="D10" s="261"/>
-      <c r="E10" s="261"/>
-      <c r="F10" s="261"/>
+      <c r="C10" s="181"/>
+      <c r="D10" s="181"/>
+      <c r="E10" s="181"/>
+      <c r="F10" s="181"/>
       <c r="H10" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="I10" s="261"/>
-      <c r="J10" s="262"/>
-      <c r="K10" s="262"/>
-      <c r="L10" s="263"/>
-    </row>
-    <row r="11" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I10" s="181"/>
+      <c r="J10" s="182"/>
+      <c r="K10" s="182"/>
+      <c r="L10" s="183"/>
+    </row>
+    <row r="11" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H11" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="I11" s="261"/>
-      <c r="J11" s="262"/>
-      <c r="K11" s="262"/>
-      <c r="L11" s="263"/>
-    </row>
-    <row r="12" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I11" s="181"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="182"/>
+      <c r="L11" s="183"/>
+    </row>
+    <row r="12" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="14"/>
       <c r="H12" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="I12" s="261"/>
-      <c r="J12" s="262"/>
-      <c r="K12" s="262"/>
-      <c r="L12" s="263"/>
+      <c r="I12" s="181"/>
+      <c r="J12" s="182"/>
+      <c r="K12" s="182"/>
+      <c r="L12" s="183"/>
     </row>
     <row r="13" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="15"/>
@@ -6120,14 +6198,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="271"/>
-      <c r="B15" s="272" t="s">
+    <row r="15" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="191"/>
+      <c r="B15" s="192" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="278"/>
-      <c r="D15" s="278"/>
-      <c r="E15" s="279"/>
+      <c r="C15" s="281"/>
+      <c r="D15" s="281"/>
+      <c r="E15" s="282"/>
       <c r="F15" s="127"/>
       <c r="G15" s="127"/>
       <c r="H15" s="127"/>
@@ -6139,14 +6217,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="271"/>
-      <c r="B16" s="264" t="s">
+    <row r="16" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="191"/>
+      <c r="B16" s="184" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="265"/>
-      <c r="D16" s="265"/>
-      <c r="E16" s="277"/>
+      <c r="C16" s="185"/>
+      <c r="D16" s="185"/>
+      <c r="E16" s="280"/>
       <c r="F16" s="127"/>
       <c r="G16" s="127"/>
       <c r="H16" s="127"/>
@@ -6158,13 +6236,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="264" t="s">
+    <row r="17" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="184" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="265"/>
-      <c r="D17" s="265"/>
-      <c r="E17" s="277"/>
+      <c r="C17" s="185"/>
+      <c r="D17" s="185"/>
+      <c r="E17" s="280"/>
       <c r="F17" s="127"/>
       <c r="G17" s="127"/>
       <c r="H17" s="127"/>
@@ -6176,13 +6254,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="276" t="s">
+    <row r="18" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="279" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="282"/>
-      <c r="D18" s="282"/>
-      <c r="E18" s="283"/>
+      <c r="C18" s="285"/>
+      <c r="D18" s="285"/>
+      <c r="E18" s="286"/>
       <c r="F18" s="127"/>
       <c r="G18" s="127"/>
       <c r="H18" s="127"/>
@@ -6194,13 +6272,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="264" t="s">
+    <row r="19" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="184" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="265"/>
-      <c r="D19" s="265"/>
-      <c r="E19" s="277"/>
+      <c r="C19" s="185"/>
+      <c r="D19" s="185"/>
+      <c r="E19" s="280"/>
       <c r="F19" s="127"/>
       <c r="G19" s="127"/>
       <c r="H19" s="127"/>
@@ -6212,13 +6290,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="264" t="s">
+    <row r="20" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="184" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="265"/>
-      <c r="D20" s="265"/>
-      <c r="E20" s="277"/>
+      <c r="C20" s="185"/>
+      <c r="D20" s="185"/>
+      <c r="E20" s="280"/>
       <c r="F20" s="127"/>
       <c r="G20" s="127"/>
       <c r="H20" s="127"/>
@@ -6230,13 +6308,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="264" t="s">
+    <row r="21" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="184" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="265"/>
-      <c r="D21" s="265"/>
-      <c r="E21" s="277"/>
+      <c r="C21" s="185"/>
+      <c r="D21" s="185"/>
+      <c r="E21" s="280"/>
       <c r="F21" s="127"/>
       <c r="G21" s="127"/>
       <c r="H21" s="127"/>
@@ -6249,12 +6327,12 @@
       </c>
     </row>
     <row r="22" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="280" t="s">
-        <v>126</v>
-      </c>
-      <c r="C22" s="281"/>
-      <c r="D22" s="281"/>
-      <c r="E22" s="281"/>
+      <c r="B22" s="283" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" s="284"/>
+      <c r="D22" s="284"/>
+      <c r="E22" s="284"/>
       <c r="F22" s="127"/>
       <c r="G22" s="127"/>
       <c r="H22" s="127"/>
@@ -6417,30 +6495,30 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:L42"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="12.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1328125" style="1"/>
-    <col min="3" max="3" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="1" customWidth="1"/>
-    <col min="5" max="7" width="7.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.08984375" style="1"/>
+    <col min="3" max="3" width="12.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.7265625" style="1" customWidth="1"/>
+    <col min="5" max="7" width="7.26953125" style="1" customWidth="1"/>
     <col min="8" max="8" width="7" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.265625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="4.73046875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.265625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.73046875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7.265625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.1328125" style="1"/>
+    <col min="9" max="9" width="7.26953125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="4.7265625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.26953125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7265625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.26953125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="11"/>
@@ -6448,11 +6526,11 @@
     </row>
     <row r="3" spans="1:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J3" s="10"/>
       <c r="K3" s="11"/>
@@ -6469,7 +6547,7 @@
       <c r="F4" s="8"/>
       <c r="H4" s="9"/>
       <c r="I4" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J4" s="10"/>
       <c r="K4" s="11"/>
@@ -6480,10 +6558,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="12"/>
-      <c r="C5" s="261"/>
-      <c r="D5" s="261"/>
-      <c r="E5" s="261"/>
-      <c r="F5" s="261"/>
+      <c r="C5" s="181"/>
+      <c r="D5" s="181"/>
+      <c r="E5" s="181"/>
+      <c r="F5" s="181"/>
       <c r="H5" s="9"/>
       <c r="I5" s="13" t="s">
         <v>10</v>
@@ -6497,17 +6575,17 @@
         <v>13</v>
       </c>
       <c r="B6" s="12"/>
-      <c r="C6" s="261"/>
-      <c r="D6" s="261"/>
-      <c r="E6" s="261"/>
-      <c r="F6" s="261"/>
+      <c r="C6" s="181"/>
+      <c r="D6" s="181"/>
+      <c r="E6" s="181"/>
+      <c r="F6" s="181"/>
       <c r="H6" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="70"/>
@@ -6517,79 +6595,79 @@
       <c r="H7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I7" s="266"/>
-      <c r="J7" s="267"/>
-      <c r="K7" s="267"/>
-      <c r="L7" s="268"/>
-    </row>
-    <row r="8" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="186"/>
+      <c r="J7" s="187"/>
+      <c r="K7" s="187"/>
+      <c r="L7" s="188"/>
+    </row>
+    <row r="8" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="266"/>
-      <c r="D8" s="266"/>
-      <c r="E8" s="266"/>
-      <c r="F8" s="266"/>
+      <c r="C8" s="186"/>
+      <c r="D8" s="186"/>
+      <c r="E8" s="186"/>
+      <c r="F8" s="186"/>
       <c r="H8" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="I8" s="261"/>
-      <c r="J8" s="262"/>
-      <c r="K8" s="262"/>
-      <c r="L8" s="263"/>
-    </row>
-    <row r="9" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I8" s="181"/>
+      <c r="J8" s="182"/>
+      <c r="K8" s="182"/>
+      <c r="L8" s="183"/>
+    </row>
+    <row r="9" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="12"/>
-      <c r="C9" s="261"/>
-      <c r="D9" s="261"/>
-      <c r="E9" s="261"/>
-      <c r="F9" s="261"/>
+      <c r="C9" s="181"/>
+      <c r="D9" s="181"/>
+      <c r="E9" s="181"/>
+      <c r="F9" s="181"/>
       <c r="H9" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="I9" s="261"/>
-      <c r="J9" s="262"/>
-      <c r="K9" s="262"/>
-      <c r="L9" s="263"/>
-    </row>
-    <row r="10" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I9" s="181"/>
+      <c r="J9" s="182"/>
+      <c r="K9" s="182"/>
+      <c r="L9" s="183"/>
+    </row>
+    <row r="10" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B10" s="12"/>
-      <c r="C10" s="261"/>
-      <c r="D10" s="261"/>
-      <c r="E10" s="261"/>
-      <c r="F10" s="261"/>
+      <c r="C10" s="181"/>
+      <c r="D10" s="181"/>
+      <c r="E10" s="181"/>
+      <c r="F10" s="181"/>
       <c r="H10" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="I10" s="261"/>
-      <c r="J10" s="262"/>
-      <c r="K10" s="262"/>
-      <c r="L10" s="263"/>
-    </row>
-    <row r="11" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I10" s="181"/>
+      <c r="J10" s="182"/>
+      <c r="K10" s="182"/>
+      <c r="L10" s="183"/>
+    </row>
+    <row r="11" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H11" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="I11" s="261"/>
-      <c r="J11" s="262"/>
-      <c r="K11" s="262"/>
-      <c r="L11" s="263"/>
-    </row>
-    <row r="12" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I11" s="181"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="182"/>
+      <c r="L11" s="183"/>
+    </row>
+    <row r="12" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H12" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="I12" s="261"/>
-      <c r="J12" s="262"/>
-      <c r="K12" s="262"/>
-      <c r="L12" s="263"/>
+      <c r="I12" s="181"/>
+      <c r="J12" s="182"/>
+      <c r="K12" s="182"/>
+      <c r="L12" s="183"/>
     </row>
     <row r="13" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H13" s="3"/>
@@ -6598,7 +6676,7 @@
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
     </row>
-    <row r="14" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="52" t="s">
         <v>20</v>
       </c>
@@ -6639,24 +6717,24 @@
       <c r="K17" s="109"/>
       <c r="L17" s="110"/>
     </row>
-    <row r="18" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G19" s="26"/>
       <c r="H19" s="100" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I19" s="56"/>
       <c r="K19" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="88" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C20" s="47"/>
       <c r="D20" s="61"/>
@@ -6675,7 +6753,7 @@
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="88" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C21" s="47"/>
       <c r="D21" s="61"/>
@@ -6694,7 +6772,7 @@
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="88" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C22" s="47"/>
       <c r="D22" s="61"/>
@@ -6711,9 +6789,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="12.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" ht="14" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C23" s="48"/>
       <c r="D23" s="48"/>
@@ -6728,9 +6806,9 @@
       <c r="J23" s="21"/>
       <c r="K23" s="21"/>
     </row>
-    <row r="24" spans="1:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G24" s="72" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H24" s="10"/>
       <c r="I24" s="10"/>
@@ -6745,7 +6823,7 @@
     </row>
     <row r="25" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -6762,13 +6840,13 @@
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="47" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C27" s="48"/>
       <c r="D27" s="61"/>
       <c r="E27" s="128"/>
       <c r="F27" s="47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G27" s="61"/>
       <c r="H27" s="63">
@@ -6819,7 +6897,7 @@
     </row>
     <row r="32" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G32" s="72" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H32" s="10"/>
       <c r="I32" s="10"/>
@@ -6835,7 +6913,7 @@
     <row r="33" spans="1:12" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="34" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I34" s="49" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J34" s="76"/>
       <c r="K34" s="76"/>
@@ -6898,30 +6976,30 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L42"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="12.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1328125" style="1"/>
-    <col min="3" max="3" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="0.6640625" style="1" customWidth="1"/>
-    <col min="5" max="7" width="7.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.08984375" style="1"/>
+    <col min="3" max="3" width="12.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="0.6328125" style="1" customWidth="1"/>
+    <col min="5" max="7" width="7.26953125" style="1" customWidth="1"/>
     <col min="8" max="8" width="7" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.265625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.33203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.265625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.73046875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7.265625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.1328125" style="1"/>
+    <col min="9" max="9" width="7.26953125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.36328125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.26953125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7265625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.26953125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="11"/>
@@ -6929,11 +7007,11 @@
     </row>
     <row r="3" spans="1:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J3" s="10"/>
       <c r="K3" s="11"/>
@@ -6950,7 +7028,7 @@
       <c r="F4" s="8"/>
       <c r="H4" s="9"/>
       <c r="I4" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J4" s="10"/>
       <c r="K4" s="11"/>
@@ -6961,10 +7039,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="12"/>
-      <c r="C5" s="261"/>
-      <c r="D5" s="261"/>
-      <c r="E5" s="261"/>
-      <c r="F5" s="261"/>
+      <c r="C5" s="181"/>
+      <c r="D5" s="181"/>
+      <c r="E5" s="181"/>
+      <c r="F5" s="181"/>
       <c r="H5" s="9"/>
       <c r="I5" s="13" t="s">
         <v>10</v>
@@ -6978,17 +7056,17 @@
         <v>13</v>
       </c>
       <c r="B6" s="12"/>
-      <c r="C6" s="261"/>
-      <c r="D6" s="261"/>
-      <c r="E6" s="261"/>
-      <c r="F6" s="261"/>
+      <c r="C6" s="181"/>
+      <c r="D6" s="181"/>
+      <c r="E6" s="181"/>
+      <c r="F6" s="181"/>
       <c r="H6" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="70"/>
@@ -6998,79 +7076,79 @@
       <c r="H7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I7" s="266"/>
-      <c r="J7" s="267"/>
-      <c r="K7" s="267"/>
-      <c r="L7" s="268"/>
-    </row>
-    <row r="8" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="186"/>
+      <c r="J7" s="187"/>
+      <c r="K7" s="187"/>
+      <c r="L7" s="188"/>
+    </row>
+    <row r="8" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="266"/>
-      <c r="D8" s="266"/>
-      <c r="E8" s="266"/>
-      <c r="F8" s="266"/>
+      <c r="C8" s="186"/>
+      <c r="D8" s="186"/>
+      <c r="E8" s="186"/>
+      <c r="F8" s="186"/>
       <c r="H8" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="I8" s="261"/>
-      <c r="J8" s="262"/>
-      <c r="K8" s="262"/>
-      <c r="L8" s="263"/>
-    </row>
-    <row r="9" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I8" s="181"/>
+      <c r="J8" s="182"/>
+      <c r="K8" s="182"/>
+      <c r="L8" s="183"/>
+    </row>
+    <row r="9" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="12"/>
-      <c r="C9" s="261"/>
-      <c r="D9" s="261"/>
-      <c r="E9" s="261"/>
-      <c r="F9" s="261"/>
+      <c r="C9" s="181"/>
+      <c r="D9" s="181"/>
+      <c r="E9" s="181"/>
+      <c r="F9" s="181"/>
       <c r="H9" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="I9" s="261"/>
-      <c r="J9" s="262"/>
-      <c r="K9" s="262"/>
-      <c r="L9" s="263"/>
-    </row>
-    <row r="10" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I9" s="181"/>
+      <c r="J9" s="182"/>
+      <c r="K9" s="182"/>
+      <c r="L9" s="183"/>
+    </row>
+    <row r="10" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B10" s="12"/>
-      <c r="C10" s="261"/>
-      <c r="D10" s="261"/>
-      <c r="E10" s="261"/>
-      <c r="F10" s="261"/>
+      <c r="C10" s="181"/>
+      <c r="D10" s="181"/>
+      <c r="E10" s="181"/>
+      <c r="F10" s="181"/>
       <c r="H10" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="I10" s="261"/>
-      <c r="J10" s="262"/>
-      <c r="K10" s="262"/>
-      <c r="L10" s="263"/>
-    </row>
-    <row r="11" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I10" s="181"/>
+      <c r="J10" s="182"/>
+      <c r="K10" s="182"/>
+      <c r="L10" s="183"/>
+    </row>
+    <row r="11" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H11" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="I11" s="261"/>
-      <c r="J11" s="262"/>
-      <c r="K11" s="262"/>
-      <c r="L11" s="263"/>
-    </row>
-    <row r="12" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I11" s="181"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="182"/>
+      <c r="L11" s="183"/>
+    </row>
+    <row r="12" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H12" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="I12" s="261"/>
-      <c r="J12" s="262"/>
-      <c r="K12" s="262"/>
-      <c r="L12" s="263"/>
+      <c r="I12" s="181"/>
+      <c r="J12" s="182"/>
+      <c r="K12" s="182"/>
+      <c r="L12" s="183"/>
     </row>
     <row r="13" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H13" s="3"/>
@@ -7079,7 +7157,7 @@
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
     </row>
-    <row r="14" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="52" t="s">
         <v>20</v>
       </c>
@@ -7096,32 +7174,32 @@
       <c r="L14" s="54"/>
     </row>
     <row r="15" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="284"/>
-      <c r="B15" s="285"/>
-      <c r="C15" s="285"/>
-      <c r="D15" s="285"/>
-      <c r="E15" s="285"/>
-      <c r="F15" s="285"/>
-      <c r="G15" s="285"/>
-      <c r="H15" s="285"/>
-      <c r="I15" s="285"/>
-      <c r="J15" s="285"/>
-      <c r="K15" s="285"/>
-      <c r="L15" s="286"/>
+      <c r="A15" s="287"/>
+      <c r="B15" s="288"/>
+      <c r="C15" s="288"/>
+      <c r="D15" s="288"/>
+      <c r="E15" s="288"/>
+      <c r="F15" s="288"/>
+      <c r="G15" s="288"/>
+      <c r="H15" s="288"/>
+      <c r="I15" s="288"/>
+      <c r="J15" s="288"/>
+      <c r="K15" s="288"/>
+      <c r="L15" s="289"/>
     </row>
     <row r="16" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="287"/>
-      <c r="B16" s="267"/>
-      <c r="C16" s="267"/>
-      <c r="D16" s="267"/>
-      <c r="E16" s="267"/>
-      <c r="F16" s="267"/>
-      <c r="G16" s="267"/>
-      <c r="H16" s="267"/>
-      <c r="I16" s="267"/>
-      <c r="J16" s="267"/>
-      <c r="K16" s="267"/>
-      <c r="L16" s="268"/>
+      <c r="A16" s="290"/>
+      <c r="B16" s="187"/>
+      <c r="C16" s="187"/>
+      <c r="D16" s="187"/>
+      <c r="E16" s="187"/>
+      <c r="F16" s="187"/>
+      <c r="G16" s="187"/>
+      <c r="H16" s="187"/>
+      <c r="I16" s="187"/>
+      <c r="J16" s="187"/>
+      <c r="K16" s="187"/>
+      <c r="L16" s="188"/>
     </row>
     <row r="17" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="107" t="s">
@@ -7139,24 +7217,24 @@
       <c r="K17" s="109"/>
       <c r="L17" s="110"/>
     </row>
-    <row r="18" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G19" s="26"/>
       <c r="H19" s="100" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I19" s="56"/>
       <c r="K19" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="88" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C20" s="47"/>
       <c r="D20" s="61"/>
@@ -7178,7 +7256,7 @@
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="88" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C21" s="47"/>
       <c r="D21" s="61"/>
@@ -7200,7 +7278,7 @@
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="88" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C22" s="47"/>
       <c r="D22" s="61"/>
@@ -7220,9 +7298,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="12.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" ht="14" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C23" s="48"/>
       <c r="D23" s="48"/>
@@ -7237,9 +7315,9 @@
       <c r="J23" s="21"/>
       <c r="K23" s="21"/>
     </row>
-    <row r="24" spans="1:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G24" s="72" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H24" s="10"/>
       <c r="I24" s="10"/>
@@ -7254,7 +7332,7 @@
     </row>
     <row r="25" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -7271,7 +7349,7 @@
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="47" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C27" s="48"/>
       <c r="D27" s="61"/>
@@ -7281,7 +7359,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G27" s="61"/>
       <c r="H27" s="63">
@@ -7335,7 +7413,7 @@
     </row>
     <row r="32" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G32" s="72" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H32" s="10"/>
       <c r="I32" s="10"/>
@@ -7351,7 +7429,7 @@
     <row r="33" spans="1:12" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="34" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I34" s="49" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J34" s="76"/>
       <c r="K34" s="76"/>
@@ -7416,30 +7494,30 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:L42"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="12.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1328125" style="1"/>
-    <col min="3" max="3" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="1" customWidth="1"/>
-    <col min="5" max="7" width="7.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.08984375" style="1"/>
+    <col min="3" max="3" width="12.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.7265625" style="1" customWidth="1"/>
+    <col min="5" max="7" width="7.26953125" style="1" customWidth="1"/>
     <col min="8" max="8" width="7" style="1" customWidth="1"/>
-    <col min="9" max="9" width="5.9296875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="6.3984375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.265625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.73046875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7.265625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.1328125" style="1"/>
+    <col min="9" max="9" width="6.6328125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="6.36328125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.26953125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7265625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.26953125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="11"/>
@@ -7447,11 +7525,11 @@
     </row>
     <row r="3" spans="1:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J3" s="10"/>
       <c r="K3" s="11"/>
@@ -7468,7 +7546,7 @@
       <c r="F4" s="8"/>
       <c r="H4" s="9"/>
       <c r="I4" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J4" s="10"/>
       <c r="K4" s="11"/>
@@ -7479,10 +7557,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="12"/>
-      <c r="C5" s="261"/>
-      <c r="D5" s="261"/>
-      <c r="E5" s="261"/>
-      <c r="F5" s="261"/>
+      <c r="C5" s="181"/>
+      <c r="D5" s="181"/>
+      <c r="E5" s="181"/>
+      <c r="F5" s="181"/>
       <c r="H5" s="9"/>
       <c r="I5" s="13" t="s">
         <v>10</v>
@@ -7496,17 +7574,17 @@
         <v>13</v>
       </c>
       <c r="B6" s="12"/>
-      <c r="C6" s="261"/>
-      <c r="D6" s="261"/>
-      <c r="E6" s="261"/>
-      <c r="F6" s="261"/>
+      <c r="C6" s="181"/>
+      <c r="D6" s="181"/>
+      <c r="E6" s="181"/>
+      <c r="F6" s="181"/>
       <c r="H6" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="70"/>
@@ -7516,79 +7594,79 @@
       <c r="H7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I7" s="266"/>
-      <c r="J7" s="267"/>
-      <c r="K7" s="267"/>
-      <c r="L7" s="268"/>
-    </row>
-    <row r="8" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="186"/>
+      <c r="J7" s="187"/>
+      <c r="K7" s="187"/>
+      <c r="L7" s="188"/>
+    </row>
+    <row r="8" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="266"/>
-      <c r="D8" s="266"/>
-      <c r="E8" s="266"/>
-      <c r="F8" s="266"/>
+      <c r="C8" s="186"/>
+      <c r="D8" s="186"/>
+      <c r="E8" s="186"/>
+      <c r="F8" s="186"/>
       <c r="H8" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="I8" s="261"/>
-      <c r="J8" s="262"/>
-      <c r="K8" s="262"/>
-      <c r="L8" s="263"/>
-    </row>
-    <row r="9" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I8" s="181"/>
+      <c r="J8" s="182"/>
+      <c r="K8" s="182"/>
+      <c r="L8" s="183"/>
+    </row>
+    <row r="9" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="12"/>
-      <c r="C9" s="261"/>
-      <c r="D9" s="261"/>
-      <c r="E9" s="261"/>
-      <c r="F9" s="261"/>
+      <c r="C9" s="181"/>
+      <c r="D9" s="181"/>
+      <c r="E9" s="181"/>
+      <c r="F9" s="181"/>
       <c r="H9" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="I9" s="261"/>
-      <c r="J9" s="262"/>
-      <c r="K9" s="262"/>
-      <c r="L9" s="263"/>
-    </row>
-    <row r="10" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I9" s="181"/>
+      <c r="J9" s="182"/>
+      <c r="K9" s="182"/>
+      <c r="L9" s="183"/>
+    </row>
+    <row r="10" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B10" s="12"/>
-      <c r="C10" s="261"/>
-      <c r="D10" s="261"/>
-      <c r="E10" s="261"/>
-      <c r="F10" s="261"/>
+      <c r="C10" s="181"/>
+      <c r="D10" s="181"/>
+      <c r="E10" s="181"/>
+      <c r="F10" s="181"/>
       <c r="H10" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="I10" s="261"/>
-      <c r="J10" s="262"/>
-      <c r="K10" s="262"/>
-      <c r="L10" s="263"/>
-    </row>
-    <row r="11" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I10" s="181"/>
+      <c r="J10" s="182"/>
+      <c r="K10" s="182"/>
+      <c r="L10" s="183"/>
+    </row>
+    <row r="11" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H11" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="I11" s="261"/>
-      <c r="J11" s="262"/>
-      <c r="K11" s="262"/>
-      <c r="L11" s="263"/>
-    </row>
-    <row r="12" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I11" s="181"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="182"/>
+      <c r="L11" s="183"/>
+    </row>
+    <row r="12" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H12" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="I12" s="261"/>
-      <c r="J12" s="262"/>
-      <c r="K12" s="262"/>
-      <c r="L12" s="263"/>
+      <c r="I12" s="181"/>
+      <c r="J12" s="182"/>
+      <c r="K12" s="182"/>
+      <c r="L12" s="183"/>
     </row>
     <row r="13" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H13" s="3"/>
@@ -7597,7 +7675,7 @@
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
     </row>
-    <row r="14" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="52" t="s">
         <v>20</v>
       </c>
@@ -7614,32 +7692,32 @@
       <c r="L14" s="54"/>
     </row>
     <row r="15" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="284"/>
-      <c r="B15" s="285"/>
-      <c r="C15" s="285"/>
-      <c r="D15" s="285"/>
-      <c r="E15" s="285"/>
-      <c r="F15" s="285"/>
-      <c r="G15" s="285"/>
-      <c r="H15" s="285"/>
-      <c r="I15" s="285"/>
-      <c r="J15" s="285"/>
-      <c r="K15" s="285"/>
-      <c r="L15" s="286"/>
+      <c r="A15" s="287"/>
+      <c r="B15" s="288"/>
+      <c r="C15" s="288"/>
+      <c r="D15" s="288"/>
+      <c r="E15" s="288"/>
+      <c r="F15" s="288"/>
+      <c r="G15" s="288"/>
+      <c r="H15" s="288"/>
+      <c r="I15" s="288"/>
+      <c r="J15" s="288"/>
+      <c r="K15" s="288"/>
+      <c r="L15" s="289"/>
     </row>
     <row r="16" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="287"/>
-      <c r="B16" s="267"/>
-      <c r="C16" s="267"/>
-      <c r="D16" s="267"/>
-      <c r="E16" s="267"/>
-      <c r="F16" s="267"/>
-      <c r="G16" s="267"/>
-      <c r="H16" s="267"/>
-      <c r="I16" s="267"/>
-      <c r="J16" s="267"/>
-      <c r="K16" s="267"/>
-      <c r="L16" s="268"/>
+      <c r="A16" s="290"/>
+      <c r="B16" s="187"/>
+      <c r="C16" s="187"/>
+      <c r="D16" s="187"/>
+      <c r="E16" s="187"/>
+      <c r="F16" s="187"/>
+      <c r="G16" s="187"/>
+      <c r="H16" s="187"/>
+      <c r="I16" s="187"/>
+      <c r="J16" s="187"/>
+      <c r="K16" s="187"/>
+      <c r="L16" s="188"/>
     </row>
     <row r="17" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="107" t="s">
@@ -7669,24 +7747,24 @@
       <c r="K17" s="109"/>
       <c r="L17" s="110"/>
     </row>
-    <row r="18" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G19" s="26"/>
       <c r="H19" s="87" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I19" s="56"/>
       <c r="K19" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="88" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C20" s="47"/>
       <c r="D20" s="61"/>
@@ -7712,7 +7790,7 @@
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="88" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C21" s="47"/>
       <c r="D21" s="61"/>
@@ -7738,7 +7816,7 @@
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="88" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C22" s="47"/>
       <c r="D22" s="61"/>
@@ -7762,9 +7840,9 @@
       </c>
       <c r="L22" s="21"/>
     </row>
-    <row r="23" spans="1:12" ht="12.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" ht="14" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C23" s="48"/>
       <c r="D23" s="48"/>
@@ -7787,7 +7865,7 @@
       <c r="E24" s="92"/>
       <c r="F24" s="92"/>
       <c r="G24" s="94" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H24" s="95"/>
       <c r="I24" s="95"/>
@@ -7815,7 +7893,7 @@
     </row>
     <row r="26" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -7832,7 +7910,7 @@
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="47" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28" s="48"/>
       <c r="D28" s="61"/>
@@ -7842,7 +7920,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G28" s="61"/>
       <c r="H28" s="63">
@@ -7896,7 +7974,7 @@
     </row>
     <row r="33" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G33" s="72" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H33" s="10"/>
       <c r="I33" s="10"/>
@@ -7912,7 +7990,7 @@
     <row r="34" spans="1:12" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="35" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I35" s="49" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J35" s="76"/>
       <c r="K35" s="76"/>
@@ -7970,30 +8048,30 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="12.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1328125" style="1"/>
-    <col min="3" max="3" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="1" customWidth="1"/>
-    <col min="5" max="7" width="7.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.36328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.08984375" style="1"/>
+    <col min="3" max="3" width="12.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.7265625" style="1" customWidth="1"/>
+    <col min="5" max="7" width="7.26953125" style="1" customWidth="1"/>
     <col min="8" max="8" width="7" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.265625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="4.73046875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.265625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.73046875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7.265625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.1328125" style="1"/>
+    <col min="9" max="9" width="7.26953125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="4.7265625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.26953125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7265625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.26953125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:13" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="11"/>
@@ -8001,11 +8079,11 @@
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J3" s="10"/>
       <c r="K3" s="11"/>
@@ -8022,7 +8100,7 @@
       <c r="F4" s="8"/>
       <c r="H4" s="9"/>
       <c r="I4" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J4" s="10"/>
       <c r="K4" s="11"/>
@@ -8033,10 +8111,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="12"/>
-      <c r="C5" s="261"/>
-      <c r="D5" s="261"/>
-      <c r="E5" s="261"/>
-      <c r="F5" s="261"/>
+      <c r="C5" s="181"/>
+      <c r="D5" s="181"/>
+      <c r="E5" s="181"/>
+      <c r="F5" s="181"/>
       <c r="H5" s="9"/>
       <c r="I5" s="13" t="s">
         <v>10</v>
@@ -8050,17 +8128,17 @@
         <v>13</v>
       </c>
       <c r="B6" s="12"/>
-      <c r="C6" s="261"/>
-      <c r="D6" s="261"/>
-      <c r="E6" s="261"/>
-      <c r="F6" s="261"/>
+      <c r="C6" s="181"/>
+      <c r="D6" s="181"/>
+      <c r="E6" s="181"/>
+      <c r="F6" s="181"/>
       <c r="H6" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="70"/>
@@ -8070,80 +8148,80 @@
       <c r="H7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I7" s="266"/>
-      <c r="J7" s="267"/>
-      <c r="K7" s="267"/>
-      <c r="L7" s="268"/>
-    </row>
-    <row r="8" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="186"/>
+      <c r="J7" s="187"/>
+      <c r="K7" s="187"/>
+      <c r="L7" s="188"/>
+    </row>
+    <row r="8" spans="1:13" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="266"/>
-      <c r="D8" s="266"/>
-      <c r="E8" s="266"/>
-      <c r="F8" s="266"/>
+      <c r="C8" s="186"/>
+      <c r="D8" s="186"/>
+      <c r="E8" s="186"/>
+      <c r="F8" s="186"/>
       <c r="H8" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="I8" s="261"/>
-      <c r="J8" s="262"/>
-      <c r="K8" s="262"/>
-      <c r="L8" s="263"/>
-    </row>
-    <row r="9" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I8" s="181"/>
+      <c r="J8" s="182"/>
+      <c r="K8" s="182"/>
+      <c r="L8" s="183"/>
+    </row>
+    <row r="9" spans="1:13" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="12"/>
-      <c r="C9" s="261"/>
-      <c r="D9" s="261"/>
-      <c r="E9" s="261"/>
-      <c r="F9" s="261"/>
+      <c r="C9" s="181"/>
+      <c r="D9" s="181"/>
+      <c r="E9" s="181"/>
+      <c r="F9" s="181"/>
       <c r="H9" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="I9" s="261"/>
-      <c r="J9" s="262"/>
-      <c r="K9" s="262"/>
-      <c r="L9" s="263"/>
-    </row>
-    <row r="10" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I9" s="181"/>
+      <c r="J9" s="182"/>
+      <c r="K9" s="182"/>
+      <c r="L9" s="183"/>
+    </row>
+    <row r="10" spans="1:13" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B10" s="12"/>
-      <c r="C10" s="261"/>
-      <c r="D10" s="261"/>
-      <c r="E10" s="261"/>
-      <c r="F10" s="261"/>
+      <c r="C10" s="181"/>
+      <c r="D10" s="181"/>
+      <c r="E10" s="181"/>
+      <c r="F10" s="181"/>
       <c r="H10" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="I10" s="261"/>
-      <c r="J10" s="262"/>
-      <c r="K10" s="262"/>
-      <c r="L10" s="263"/>
-    </row>
-    <row r="11" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I10" s="181"/>
+      <c r="J10" s="182"/>
+      <c r="K10" s="182"/>
+      <c r="L10" s="183"/>
+    </row>
+    <row r="11" spans="1:13" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H11" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="I11" s="261"/>
-      <c r="J11" s="262"/>
-      <c r="K11" s="262"/>
-      <c r="L11" s="263"/>
-    </row>
-    <row r="12" spans="1:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I11" s="181"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="182"/>
+      <c r="L11" s="183"/>
+    </row>
+    <row r="12" spans="1:13" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="14"/>
       <c r="H12" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="I12" s="261"/>
-      <c r="J12" s="262"/>
-      <c r="K12" s="262"/>
-      <c r="L12" s="263"/>
+      <c r="I12" s="181"/>
+      <c r="J12" s="182"/>
+      <c r="K12" s="182"/>
+      <c r="L12" s="183"/>
     </row>
     <row r="13" spans="1:13" ht="8.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="14"/>
@@ -8157,25 +8235,25 @@
       <c r="C14" s="14"/>
       <c r="I14" s="66"/>
       <c r="K14" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="172" t="s">
+        <v>125</v>
+      </c>
+      <c r="B15" s="291" t="s">
+        <v>126</v>
+      </c>
+      <c r="C15" s="292"/>
+      <c r="D15" s="292"/>
+      <c r="E15" s="292"/>
+      <c r="F15" s="292"/>
+      <c r="G15" s="292"/>
+      <c r="H15" s="292"/>
+      <c r="I15" s="293"/>
+      <c r="J15" s="173" t="s">
         <v>127</v>
-      </c>
-      <c r="B15" s="288" t="s">
-        <v>128</v>
-      </c>
-      <c r="C15" s="289"/>
-      <c r="D15" s="289"/>
-      <c r="E15" s="289"/>
-      <c r="F15" s="289"/>
-      <c r="G15" s="289"/>
-      <c r="H15" s="289"/>
-      <c r="I15" s="290"/>
-      <c r="J15" s="173" t="s">
-        <v>129</v>
       </c>
       <c r="K15" s="174"/>
       <c r="L15" s="175">
@@ -8184,21 +8262,21 @@
       </c>
     </row>
     <row r="16" spans="1:13" ht="66.400000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="291" t="s">
+      <c r="A16" s="294" t="s">
+        <v>141</v>
+      </c>
+      <c r="B16" s="298" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="299"/>
+      <c r="D16" s="299"/>
+      <c r="E16" s="299"/>
+      <c r="F16" s="299"/>
+      <c r="G16" s="299"/>
+      <c r="H16" s="299"/>
+      <c r="I16" s="299"/>
+      <c r="J16" s="78" t="s">
         <v>143</v>
-      </c>
-      <c r="B16" s="295" t="s">
-        <v>141</v>
-      </c>
-      <c r="C16" s="296"/>
-      <c r="D16" s="296"/>
-      <c r="E16" s="296"/>
-      <c r="F16" s="296"/>
-      <c r="G16" s="296"/>
-      <c r="H16" s="296"/>
-      <c r="I16" s="296"/>
-      <c r="J16" s="78" t="s">
-        <v>145</v>
       </c>
       <c r="K16" s="130"/>
       <c r="L16" s="79">
@@ -8208,19 +8286,19 @@
       <c r="M16" s="80"/>
     </row>
     <row r="17" spans="1:13" ht="83.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="292"/>
-      <c r="B17" s="295" t="s">
-        <v>142</v>
-      </c>
-      <c r="C17" s="296"/>
-      <c r="D17" s="296"/>
-      <c r="E17" s="296"/>
-      <c r="F17" s="296"/>
-      <c r="G17" s="296"/>
-      <c r="H17" s="296"/>
-      <c r="I17" s="296"/>
+      <c r="A17" s="295"/>
+      <c r="B17" s="298" t="s">
+        <v>140</v>
+      </c>
+      <c r="C17" s="299"/>
+      <c r="D17" s="299"/>
+      <c r="E17" s="299"/>
+      <c r="F17" s="299"/>
+      <c r="G17" s="299"/>
+      <c r="H17" s="299"/>
+      <c r="I17" s="299"/>
       <c r="J17" s="81" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K17" s="131"/>
       <c r="L17" s="82">
@@ -8230,21 +8308,21 @@
       <c r="M17" s="80"/>
     </row>
     <row r="18" spans="1:13" ht="58.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="293" t="s">
+      <c r="A18" s="296" t="s">
+        <v>142</v>
+      </c>
+      <c r="B18" s="300" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="301"/>
+      <c r="D18" s="301"/>
+      <c r="E18" s="301"/>
+      <c r="F18" s="301"/>
+      <c r="G18" s="301"/>
+      <c r="H18" s="301"/>
+      <c r="I18" s="302"/>
+      <c r="J18" s="78" t="s">
         <v>144</v>
-      </c>
-      <c r="B18" s="297" t="s">
-        <v>131</v>
-      </c>
-      <c r="C18" s="298"/>
-      <c r="D18" s="298"/>
-      <c r="E18" s="298"/>
-      <c r="F18" s="298"/>
-      <c r="G18" s="298"/>
-      <c r="H18" s="298"/>
-      <c r="I18" s="299"/>
-      <c r="J18" s="78" t="s">
-        <v>146</v>
       </c>
       <c r="K18" s="132"/>
       <c r="L18" s="83">
@@ -8254,19 +8332,19 @@
       <c r="M18" s="80"/>
     </row>
     <row r="19" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="294"/>
-      <c r="B19" s="300" t="s">
-        <v>132</v>
-      </c>
-      <c r="C19" s="301"/>
-      <c r="D19" s="301"/>
-      <c r="E19" s="301"/>
-      <c r="F19" s="301"/>
-      <c r="G19" s="301"/>
-      <c r="H19" s="301"/>
-      <c r="I19" s="302"/>
+      <c r="A19" s="297"/>
+      <c r="B19" s="303" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" s="304"/>
+      <c r="D19" s="304"/>
+      <c r="E19" s="304"/>
+      <c r="F19" s="304"/>
+      <c r="G19" s="304"/>
+      <c r="H19" s="304"/>
+      <c r="I19" s="305"/>
       <c r="J19" s="84" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K19" s="133"/>
       <c r="L19" s="85">
@@ -8289,7 +8367,7 @@
     </row>
     <row r="22" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="47" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22" s="61"/>
       <c r="D22" s="48"/>
@@ -8307,7 +8385,7 @@
     </row>
     <row r="24" spans="1:13" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I24" s="49" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J24" s="76"/>
       <c r="K24" s="76"/>
@@ -8372,6 +8450,24 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100570C130F412EDB4EBF3E80DF6A9149FD" ma:contentTypeVersion="1" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cfaa3b10b9be17ef9f56bd19dc71004c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ddb0c952b897a810c8a4e377cff6bff8" ns1:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -8437,25 +8533,30 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28A807C1-6DB8-4C6A-8DCB-8B5F61EFE299}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64838F1D-7ECA-4F32-944F-43492487C498}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A00BD0D-8423-4FFE-92A4-D273D2078383}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8470,27 +8571,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/internal/2005/internalDocumentation"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28A807C1-6DB8-4C6A-8DCB-8B5F61EFE299}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64838F1D-7ECA-4F32-944F-43492487C498}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>